--- a/Documentos/Planilha de Requisitos - WHIS{KEY}.xlsx
+++ b/Documentos/Planilha de Requisitos - WHIS{KEY}.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83966574-C2F9-4921-950D-8163E7881883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6622D939-2C9F-4AE8-80F5-E739A8873DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requisitos Projeto" sheetId="1" r:id="rId1"/>
-    <sheet name="Planilha Requisitos SP2" sheetId="3" r:id="rId2"/>
+    <sheet name="Planilha Requisitos SP2 (2)" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Requisitos Projeto'!#REF!</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="138">
   <si>
     <t>Planilha de requisitos</t>
   </si>
@@ -448,6 +448,9 @@
   </si>
   <si>
     <t>SELECIONAR MINI SPRINT (A -D)</t>
+  </si>
+  <si>
+    <t>SPRINT</t>
   </si>
 </sst>
 </file>
@@ -461,7 +464,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -676,8 +679,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Univers"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="44">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -923,8 +933,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1190,6 +1206,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1240,7 +1265,7 @@
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1380,16 +1405,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1405,9 +1436,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1428,17 +1456,26 @@
     <xf numFmtId="0" fontId="0" fillId="43" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="35" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="35" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="47">
@@ -1706,15 +1743,15 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="16"/>
-        <color theme="8" tint="-0.249977111117893"/>
+        <color rgb="FF2E653D"/>
         <name val="Univers"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="2"/>
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFDFE3E5"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="2" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2750,7 +2787,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>378</c:v>
+                  <c:v>294</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>93</c:v>
@@ -3052,379 +3089,6 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="107"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="7"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst>
-                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="40000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="stacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Requisitos Projeto'!$E$85</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Progresso</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="34925" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="lt1">
-                        <a:lumMod val="85000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="pt-BR"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="t"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="lt1">
-                          <a:lumMod val="95000"/>
-                          <a:alpha val="54000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Requisitos Projeto'!$D$86:$D$89</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>TOTAL</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v> SP1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>SP2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>SP3</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Requisitos Projeto'!$E$86:$E$89</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>378</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>285</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>84</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8DA0-4863-B23E-317C9A233EC6}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="t"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="1488008272"/>
-        <c:axId val="1488007312"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1488008272"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:lumMod val="95000"/>
-                <a:alpha val="10000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1488007312"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1488007312"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                  <a:alpha val="10000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1488008272"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="85000"/>
-            <a:lumOff val="15000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="circle">
-        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="pt-BR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="102"/>
     </mc:Choice>
     <mc:Fallback>
@@ -3510,7 +3174,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Planilha Requisitos SP2'!$D$59</c:f>
+              <c:f>'Planilha Requisitos SP2 (2)'!$D$59</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3595,7 +3259,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Planilha Requisitos SP2'!$C$60:$C$64</c:f>
+              <c:f>'Planilha Requisitos SP2 (2)'!$C$60:$C$64</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -3618,7 +3282,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Planilha Requisitos SP2'!$D$60:$D$64</c:f>
+              <c:f>'Planilha Requisitos SP2 (2)'!$D$60:$D$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -3643,7 +3307,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7237-4D56-B87A-12053D384841}"/>
+              <c16:uniqueId val="{00000000-0909-4A96-8281-E7857BEB5F3A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3866,12 +3530,6 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="18">
-  <a:schemeClr val="accent5"/>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -4903,516 +4561,20 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="233">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="10000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="65000"/>
-              <a:lumOff val="35000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="85000"/>
-              <a:lumOff val="15000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-        </a:path>
-        <a:tileRect/>
-      </a:gradFill>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="34925" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="10000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="5000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="95000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:defRPr>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>807041</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>115769</xdr:rowOff>
+      <xdr:colOff>803935</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>336294</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>9098256</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>28854</xdr:rowOff>
+      <xdr:colOff>9095150</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>241096</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5440,15 +4602,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>252704</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>77756</xdr:rowOff>
+      <xdr:colOff>329711</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>36635</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>5229030</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>416921</xdr:rowOff>
+      <xdr:colOff>4707547</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>274759</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5463,7 +4625,7 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
+      <xdr:blipFill rotWithShape="1">
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
@@ -5471,14 +4633,15 @@
             </a:ext>
           </a:extLst>
         </a:blip>
+        <a:srcRect l="7805" t="11386" r="4222" b="25275"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="547113" y="77756"/>
-          <a:ext cx="4976326" cy="2555892"/>
+          <a:off x="622788" y="293077"/>
+          <a:ext cx="4377836" cy="1630240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5490,15 +4653,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1060331</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>323491</xdr:rowOff>
+      <xdr:colOff>1081037</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>80188</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>3726114</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>179716</xdr:rowOff>
+      <xdr:colOff>3746820</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>317415</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5527,139 +4690,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1347878" y="24423538"/>
-          <a:ext cx="2665783" cy="1365848"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1060331</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>323491</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2665783" cy="1380225"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Imagem 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C78241BD-8C3B-4D64-A7F2-932796059DF4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1354740" y="23114218"/>
-          <a:ext cx="2665783" cy="1380225"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>850446</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>9523</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>9089571</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>108856</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Gráfico 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF565E72-3D61-7106-2714-A92222A76D96}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>911680</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>299358</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2435680</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>326418</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0DD653E-4818-4675-96AC-89E8068EFB51}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1197430" y="31854322"/>
-          <a:ext cx="1524000" cy="789060"/>
+          <a:off x="1366787" y="23606938"/>
+          <a:ext cx="2665783" cy="1380227"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5688,10 +4720,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Imagem 4">
+        <xdr:cNvPr id="2" name="Imagem 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E23EB46-B6B8-4847-A72B-B0BB02B50CAB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EF6979A-0C3B-4919-A75F-FAD8CD826860}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5714,7 +4746,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="320174" y="9921"/>
-          <a:ext cx="3230088" cy="1718469"/>
+          <a:ext cx="3230088" cy="1664494"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5738,14 +4770,16 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Gráfico 3">
+        <xdr:cNvPr id="3" name="Gráfico 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82AC63C1-FBC7-F782-50DE-92ADBA28BE7C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB9417DC-3A42-4BC7-A301-A55460AB6C08}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -5774,10 +4808,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Imagem 5">
+        <xdr:cNvPr id="4" name="Imagem 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBDA498A-A2B3-45FE-A1FE-A3A4EA191BF7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21F1E4CE-D8E8-4A70-B26A-C8DDCFB16752}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5799,8 +4833,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4597783" y="9732690"/>
-          <a:ext cx="1747444" cy="896137"/>
+          <a:off x="4597783" y="9682272"/>
+          <a:ext cx="1745439" cy="884678"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5814,15 +4848,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Inventory_List_Table" displayName="Inventory_List_Table" ref="B4:H57" headerRowDxfId="28" dataDxfId="27">
-  <autoFilter ref="B4:H57" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-  </autoFilter>
+  <autoFilter ref="B4:H57" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:H53">
     <sortCondition ref="H5:H53"/>
   </sortState>
@@ -5839,28 +4865,28 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Prioridade" dataDxfId="16" totalsRowDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="SP3" dataDxfId="14" totalsRowDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="SPRINT" dataDxfId="14" totalsRowDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DFEF5BB9-030F-49A9-A8A6-AC82E626FC0E}" name="Tabela3" displayName="Tabela3" ref="A9:G36" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{593759BF-DCCE-4953-BECF-ADBBD89465DB}" name="Tabela33" displayName="Tabela33" ref="A9:G36" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{1A52E22D-2CF6-4D98-A87D-1AA662C3121E}" name="Requisito" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{764E5F42-356E-4F61-BE66-B2F069497952}" name="Descrição" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{E7CD2CCE-8CD7-4445-AD40-E29C3D0E42D4}" name="Classificação" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{A86194DD-DD7C-44E4-A6F9-6B3373149526}" name="Tamanho" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{AC635265-1FFE-43F6-B229-3E1FC0B65C8F}" name="Tam(#)" dataDxfId="6">
-      <calculatedColumnFormula>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{3ABB08E5-2C9A-4690-AF45-A43E6CBFA44A}" name="Requisito" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{39D6DADD-7441-407B-9F79-BAEBC33D5AC6}" name="Descrição" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{073C81CA-2398-4795-BB59-552ED9C428B9}" name="Classificação" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{72027A84-3E52-4152-8205-086C0FF73974}" name="Tamanho" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{3E797D67-7B5C-4095-8F33-07FC6B730416}" name="Tam(#)" dataDxfId="6">
+      <calculatedColumnFormula>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{39BC7F66-6245-4FEC-82DE-24821B3D7E96}" name="Prioridade" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{38070FD4-3ECF-4C86-B9E2-D32D410C7F06}" name="Sprint" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{88DE098E-9146-48CA-B3AD-2D8D988F38DB}" name="Prioridade" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{242D26B9-0ED8-43C2-9CAB-8EFFEC9D3DFD}" name="Sprint" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6097,26 +5123,26 @@
     </row>
     <row r="2" spans="1:9" ht="110.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="23"/>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
       <c r="I2" s="23"/>
     </row>
     <row r="3" spans="1:9" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="23"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
       <c r="I3" s="23"/>
     </row>
     <row r="4" spans="1:9" s="4" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -6140,7 +5166,7 @@
         <v>6</v>
       </c>
       <c r="H4" s="34" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="I4" s="24"/>
     </row>
@@ -6596,19 +5622,19 @@
     </row>
     <row r="20" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="23"/>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="56">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6616,10 +5642,10 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>13</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="54">
         <v>1</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="54" t="s">
         <v>47</v>
       </c>
       <c r="I20" s="23"/>
@@ -7759,10 +6785,10 @@
       <c r="F61" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="G61" s="59" t="s">
+      <c r="G61" s="61" t="s">
         <v>116</v>
       </c>
-      <c r="H61" s="60"/>
+      <c r="H61" s="62"/>
       <c r="I61" s="23"/>
     </row>
     <row r="62" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7777,13 +6803,14 @@
         <v>378</v>
       </c>
       <c r="F62" s="15">
-        <f>SUM(Inventory_List_Table[Tam('#)])</f>
-        <v>378</v>
-      </c>
-      <c r="G62" s="55">
-        <v>0</v>
-      </c>
-      <c r="H62" s="56"/>
+        <f>SUM(Inventory_List_Table[Tam('#)])-E65</f>
+        <v>294</v>
+      </c>
+      <c r="G62" s="59">
+        <f>E62-F62</f>
+        <v>84</v>
+      </c>
+      <c r="H62" s="60"/>
       <c r="I62" s="23"/>
     </row>
     <row r="63" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7801,10 +6828,10 @@
         <f>SUM(F5:F19)</f>
         <v>93</v>
       </c>
-      <c r="G63" s="57">
+      <c r="G63" s="59">
         <v>0</v>
       </c>
-      <c r="H63" s="58"/>
+      <c r="H63" s="60"/>
       <c r="I63" s="23"/>
     </row>
     <row r="64" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7822,11 +6849,11 @@
         <f>SUM(F40,F46,F45,F44,F42,F41,F20:F39,F43)</f>
         <v>201</v>
       </c>
-      <c r="G64" s="57">
+      <c r="G64" s="59">
         <f>E64-F64</f>
         <v>0</v>
       </c>
-      <c r="H64" s="58"/>
+      <c r="H64" s="60"/>
       <c r="I64" s="23"/>
     </row>
     <row r="65" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7843,11 +6870,11 @@
       <c r="F65" s="11">
         <v>0</v>
       </c>
-      <c r="G65" s="57">
+      <c r="G65" s="59">
         <f>E65-F65</f>
         <v>84</v>
       </c>
-      <c r="H65" s="58"/>
+      <c r="H65" s="60"/>
       <c r="I65" s="23"/>
     </row>
     <row r="66" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8039,302 +7066,231 @@
     </row>
     <row r="83" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="23"/>
-      <c r="B83" s="29"/>
-      <c r="C83" s="29"/>
-      <c r="D83" s="30"/>
-      <c r="E83" s="30"/>
-      <c r="F83" s="30"/>
-      <c r="G83" s="30"/>
-      <c r="H83" s="30"/>
-      <c r="I83" s="23"/>
+      <c r="B83" s="53"/>
+      <c r="C83" s="53"/>
+      <c r="D83" s="53"/>
+      <c r="E83" s="53"/>
+      <c r="F83" s="53"/>
+      <c r="G83" s="53"/>
+      <c r="H83" s="53"/>
+      <c r="I83" s="53"/>
     </row>
     <row r="84" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="23"/>
-      <c r="B84" s="29"/>
-      <c r="C84" s="29"/>
-      <c r="D84" s="30"/>
-      <c r="E84" s="30"/>
-      <c r="F84" s="30"/>
-      <c r="G84" s="30"/>
-      <c r="H84" s="30"/>
-      <c r="I84" s="23"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
     </row>
     <row r="85" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="23"/>
-      <c r="B85" s="29"/>
-      <c r="C85" s="31"/>
-      <c r="D85" s="30"/>
-      <c r="E85" s="46" t="s">
-        <v>135</v>
-      </c>
-      <c r="F85" s="30"/>
-      <c r="G85" s="30"/>
-      <c r="H85" s="30"/>
-      <c r="I85" s="23"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3"/>
     </row>
     <row r="86" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="23"/>
-      <c r="B86" s="29"/>
-      <c r="C86" s="29"/>
-      <c r="D86" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="E86" s="15">
-        <f>SUM(Inventory_List_Table[Tam('#)])</f>
-        <v>378</v>
-      </c>
-      <c r="F86" s="30"/>
-      <c r="G86" s="30"/>
-      <c r="H86" s="30"/>
-      <c r="I86" s="22"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3"/>
     </row>
     <row r="87" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="23"/>
-      <c r="B87" s="29"/>
-      <c r="C87" s="29"/>
-      <c r="D87" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E87" s="13">
-        <f>E86-F63</f>
-        <v>285</v>
-      </c>
-      <c r="F87" s="30"/>
-      <c r="G87" s="30"/>
-      <c r="H87" s="30"/>
-      <c r="I87" s="23"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
     </row>
     <row r="88" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="23"/>
-      <c r="B88" s="29"/>
-      <c r="C88" s="29"/>
-      <c r="D88" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="E88" s="13">
-        <f>E87-F64</f>
-        <v>84</v>
-      </c>
-      <c r="F88" s="30"/>
-      <c r="G88" s="30"/>
-      <c r="H88" s="30"/>
-      <c r="I88" s="23"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
     </row>
     <row r="89" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="23"/>
-      <c r="B89" s="29"/>
-      <c r="C89" s="29"/>
-      <c r="D89" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E89" s="13">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="F89" s="30"/>
-      <c r="G89" s="30"/>
-      <c r="H89" s="30"/>
-      <c r="I89" s="24"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
     </row>
     <row r="90" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="23"/>
-      <c r="B90" s="29"/>
-      <c r="C90" s="32"/>
-      <c r="D90" s="30"/>
-      <c r="E90" s="30"/>
-      <c r="F90" s="30"/>
-      <c r="G90" s="30"/>
-      <c r="H90" s="30"/>
-      <c r="I90" s="23"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
     </row>
     <row r="91" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="23"/>
-      <c r="B91" s="29"/>
-      <c r="C91" s="33"/>
-      <c r="D91" s="30"/>
-      <c r="E91" s="30"/>
-      <c r="F91" s="30"/>
-      <c r="G91" s="30"/>
-      <c r="H91" s="30"/>
-      <c r="I91" s="23"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
     </row>
     <row r="92" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="23"/>
-      <c r="B92" s="29"/>
-      <c r="C92" s="33"/>
-      <c r="D92" s="30"/>
-      <c r="E92" s="30"/>
-      <c r="F92" s="30"/>
-      <c r="G92" s="30"/>
-      <c r="H92" s="30"/>
-      <c r="I92" s="23"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
     </row>
     <row r="93" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="23"/>
-      <c r="B93" s="29"/>
-      <c r="C93" s="29"/>
-      <c r="D93" s="30"/>
-      <c r="E93" s="30"/>
-      <c r="F93" s="30"/>
-      <c r="G93" s="30"/>
-      <c r="H93" s="30"/>
-      <c r="I93" s="23"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
     </row>
     <row r="94" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="23"/>
-      <c r="B94" s="29"/>
-      <c r="C94" s="29"/>
-      <c r="D94" s="30"/>
-      <c r="E94" s="30"/>
-      <c r="F94" s="30"/>
-      <c r="G94" s="30"/>
-      <c r="H94" s="30"/>
-      <c r="I94" s="23"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
     </row>
     <row r="95" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="23"/>
-      <c r="B95" s="29"/>
-      <c r="C95" s="29"/>
-      <c r="D95" s="30"/>
-      <c r="E95" s="30"/>
-      <c r="F95" s="30"/>
-      <c r="G95" s="30"/>
-      <c r="H95" s="30"/>
-      <c r="I95" s="23"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
     </row>
     <row r="96" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="23"/>
-      <c r="B96" s="29"/>
-      <c r="C96" s="29"/>
-      <c r="D96" s="30"/>
-      <c r="E96" s="30"/>
-      <c r="F96" s="30"/>
-      <c r="G96" s="30"/>
-      <c r="H96" s="30"/>
-      <c r="I96" s="23"/>
-    </row>
-    <row r="97" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="23"/>
-      <c r="B97" s="29"/>
-      <c r="C97" s="29"/>
-      <c r="D97" s="30"/>
-      <c r="E97" s="30"/>
-      <c r="F97" s="30"/>
-      <c r="G97" s="30"/>
-      <c r="H97" s="30"/>
-      <c r="I97" s="23"/>
-    </row>
-    <row r="98" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="23"/>
-      <c r="B98" s="29"/>
-      <c r="C98" s="29"/>
-      <c r="D98" s="30"/>
-      <c r="E98" s="30"/>
-      <c r="F98" s="30"/>
-      <c r="G98" s="30"/>
-      <c r="H98" s="30"/>
-      <c r="I98" s="23"/>
-    </row>
-    <row r="99" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="23"/>
-      <c r="B99" s="29"/>
-      <c r="C99" s="29"/>
-      <c r="D99" s="30"/>
-      <c r="E99" s="30"/>
-      <c r="F99" s="30"/>
-      <c r="G99" s="30"/>
-      <c r="H99" s="30"/>
-      <c r="I99" s="23"/>
-    </row>
-    <row r="100" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="23"/>
-      <c r="B100" s="29"/>
-      <c r="C100" s="29"/>
-      <c r="D100" s="30"/>
-      <c r="E100" s="30"/>
-      <c r="F100" s="30"/>
-      <c r="G100" s="30"/>
-      <c r="H100" s="30"/>
-      <c r="I100" s="23"/>
-    </row>
-    <row r="101" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="23"/>
-      <c r="B101" s="29"/>
-      <c r="C101" s="29"/>
-      <c r="D101" s="30"/>
-      <c r="E101" s="30"/>
-      <c r="F101" s="30"/>
-      <c r="G101" s="30"/>
-      <c r="H101" s="30"/>
-      <c r="I101" s="23"/>
-    </row>
-    <row r="102" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="23"/>
-      <c r="B102" s="29"/>
-      <c r="C102" s="29"/>
-      <c r="D102" s="30"/>
-      <c r="E102" s="30"/>
-      <c r="F102" s="30"/>
-      <c r="G102" s="30"/>
-      <c r="H102" s="30"/>
-      <c r="I102" s="23"/>
-    </row>
-    <row r="103" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="23"/>
-      <c r="B103" s="29"/>
-      <c r="C103" s="29"/>
-      <c r="D103" s="30"/>
-      <c r="E103" s="30"/>
-      <c r="F103" s="30"/>
-      <c r="G103" s="30"/>
-      <c r="H103" s="30"/>
-      <c r="I103" s="23"/>
-    </row>
-    <row r="104" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="23"/>
-      <c r="B104" s="29"/>
-      <c r="C104" s="29"/>
-      <c r="D104" s="30"/>
-      <c r="E104" s="30"/>
-      <c r="F104" s="30"/>
-      <c r="G104" s="30"/>
-      <c r="H104" s="30"/>
-      <c r="I104" s="23"/>
-    </row>
-    <row r="105" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="23"/>
-      <c r="B105" s="29"/>
-      <c r="C105" s="29"/>
-      <c r="D105" s="30"/>
-      <c r="E105" s="30"/>
-      <c r="F105" s="30"/>
-      <c r="G105" s="30"/>
-      <c r="H105" s="30"/>
-      <c r="I105" s="23"/>
-    </row>
-    <row r="106" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="23"/>
-      <c r="B106" s="23"/>
-      <c r="C106" s="23"/>
-      <c r="D106" s="23"/>
-      <c r="E106" s="23"/>
-      <c r="F106" s="23"/>
-      <c r="G106" s="23"/>
-      <c r="H106" s="23"/>
-      <c r="I106" s="23"/>
-    </row>
-    <row r="107" spans="1:9" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="23"/>
-      <c r="B107" s="23"/>
-      <c r="C107" s="23"/>
-      <c r="D107" s="23"/>
-      <c r="E107" s="23"/>
-      <c r="F107" s="23"/>
-      <c r="G107" s="23"/>
-      <c r="H107" s="23"/>
-      <c r="I107" s="23"/>
-    </row>
-    <row r="108" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+    </row>
+    <row r="97" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+    </row>
+    <row r="98" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+    </row>
+    <row r="99" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+    </row>
+    <row r="100" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+    </row>
+    <row r="101" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+    </row>
+    <row r="102" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+    </row>
+    <row r="103" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+    </row>
+    <row r="104" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
+      <c r="H104" s="3"/>
+    </row>
+    <row r="105" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
+      <c r="H105" s="3"/>
+    </row>
+    <row r="106" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3"/>
+    </row>
+    <row r="107" spans="2:8" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+    </row>
+    <row r="108" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
@@ -8343,7 +7299,7 @@
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
     </row>
-    <row r="109" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
@@ -8352,7 +7308,7 @@
       <c r="G109" s="3"/>
       <c r="H109" s="3"/>
     </row>
-    <row r="110" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
@@ -8361,7 +7317,7 @@
       <c r="G110" s="3"/>
       <c r="H110" s="3"/>
     </row>
-    <row r="111" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
@@ -8370,7 +7326,7 @@
       <c r="G111" s="3"/>
       <c r="H111" s="3"/>
     </row>
-    <row r="112" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
@@ -9081,17 +8037,14 @@
       <formula>#REF!=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations xWindow="1141" yWindow="341" count="8">
+  <dataValidations xWindow="1141" yWindow="341" count="7">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Insira o nome do item nesta coluna" sqref="B4" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Insira o nível de estoque de cada item nesta coluna" sqref="G4" xr:uid="{00000000-0002-0000-0000-000007000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Esse é um valor de estoque column._x000a__x000a_O valor de estoque de cada item é automaticamente calculado nesta coluna." sqref="F4" xr:uid="{00000000-0002-0000-0000-000008000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Insira a quantidade em estoque de cada item nesta coluna" sqref="E4" xr:uid="{00000000-0002-0000-0000-000009000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Insira o preço unitário de cada item nesta coluna" sqref="D4" xr:uid="{00000000-0002-0000-0000-00000A000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Insira uma descrição do item nesta coluna" sqref="C4" xr:uid="{00000000-0002-0000-0000-00000B000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Esta planilha controla o estoque dos itens listados na tabela de lista de estoque e possibilita realçar e sinalizar esses itens que já estão prontos para serem repostos. Itens descontinuados têm formatação Tachado e o texto &quot;sim&quot; na coluna correspondente." sqref="A1 I1 I86" xr:uid="{8F182C1C-C305-48BB-889F-2AD958D3312B}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Insira quantos dias faltam para realizar nova encomenda de cada item nesta coluna" sqref="H4" xr:uid="{00000000-0002-0000-0000-000006000000}">
-      <formula1>$H$5:$H$27</formula1>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Esta planilha controla o estoque dos itens listados na tabela de lista de estoque e possibilita realçar e sinalizar esses itens que já estão prontos para serem repostos. Itens descontinuados têm formatação Tachado e o texto &quot;sim&quot; na coluna correspondente." sqref="A1 I1" xr:uid="{8F182C1C-C305-48BB-889F-2AD958D3312B}"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9104,7 +8057,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85BC3CD0-F7F0-4C0E-883C-E32C34EA90D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D863DC5D-F27E-48D0-B8DF-8044B97C94FB}">
   <dimension ref="A1:G71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9228,11 +8181,11 @@
         <v>19</v>
       </c>
       <c r="E10" s="41">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>13</v>
       </c>
       <c r="F10" s="39">
@@ -9256,11 +8209,11 @@
         <v>16</v>
       </c>
       <c r="E11" s="38">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
       <c r="F11" s="36">
@@ -9284,11 +8237,11 @@
         <v>16</v>
       </c>
       <c r="E12" s="41">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
       <c r="F12" s="39">
@@ -9312,11 +8265,11 @@
         <v>19</v>
       </c>
       <c r="E13" s="38">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>13</v>
       </c>
       <c r="F13" s="36">
@@ -9340,11 +8293,11 @@
         <v>10</v>
       </c>
       <c r="E14" s="41">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>3</v>
       </c>
       <c r="F14" s="39">
@@ -9368,11 +8321,11 @@
         <v>16</v>
       </c>
       <c r="E15" s="38">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
       <c r="F15" s="36">
@@ -9396,11 +8349,11 @@
         <v>29</v>
       </c>
       <c r="E16" s="41">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
       <c r="F16" s="39">
@@ -9424,11 +8377,11 @@
         <v>29</v>
       </c>
       <c r="E17" s="38">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
       <c r="F17" s="36">
@@ -9452,11 +8405,11 @@
         <v>16</v>
       </c>
       <c r="E18" s="41">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
       <c r="F18" s="39">
@@ -9480,11 +8433,11 @@
         <v>19</v>
       </c>
       <c r="E19" s="38">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>13</v>
       </c>
       <c r="F19" s="36">
@@ -9508,11 +8461,11 @@
         <v>29</v>
       </c>
       <c r="E20" s="41">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
       <c r="F20" s="39">
@@ -9536,11 +8489,11 @@
         <v>16</v>
       </c>
       <c r="E21" s="38">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
       <c r="F21" s="36">
@@ -9564,11 +8517,11 @@
         <v>16</v>
       </c>
       <c r="E22" s="41">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
       <c r="F22" s="39">
@@ -9592,11 +8545,11 @@
         <v>16</v>
       </c>
       <c r="E23" s="38">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
       <c r="F23" s="36">
@@ -9620,11 +8573,11 @@
         <v>16</v>
       </c>
       <c r="E24" s="41">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
       <c r="F24" s="39">
@@ -9648,11 +8601,11 @@
         <v>29</v>
       </c>
       <c r="E25" s="38">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
       <c r="F25" s="36">
@@ -9676,11 +8629,11 @@
         <v>29</v>
       </c>
       <c r="E26" s="41">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
       <c r="F26" s="39">
@@ -9704,11 +8657,11 @@
         <v>29</v>
       </c>
       <c r="E27" s="38">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
       <c r="F27" s="36">
@@ -9732,11 +8685,11 @@
         <v>29</v>
       </c>
       <c r="E28" s="41">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
       <c r="F28" s="39">
@@ -9760,11 +8713,11 @@
         <v>29</v>
       </c>
       <c r="E29" s="38">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
       <c r="F29" s="36">
@@ -9788,11 +8741,11 @@
         <v>16</v>
       </c>
       <c r="E30" s="41">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
       <c r="F30" s="39">
@@ -9816,11 +8769,11 @@
         <v>10</v>
       </c>
       <c r="E31" s="38">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>3</v>
       </c>
       <c r="F31" s="36">
@@ -9844,11 +8797,11 @@
         <v>19</v>
       </c>
       <c r="E32" s="41">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>13</v>
       </c>
       <c r="F32" s="39">
@@ -9872,11 +8825,11 @@
         <v>19</v>
       </c>
       <c r="E33" s="38">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>13</v>
       </c>
       <c r="F33" s="36">
@@ -9900,11 +8853,11 @@
         <v>16</v>
       </c>
       <c r="E34" s="41">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
       <c r="F34" s="39">
@@ -9928,11 +8881,11 @@
         <v>29</v>
       </c>
       <c r="E35" s="38">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
       <c r="F35" s="36">
@@ -9956,11 +8909,11 @@
         <v>29</v>
       </c>
       <c r="E36" s="41">
-        <f>IF(Tabela3[[#This Row],[Tamanho]]="PP",3,
-IF(Tabela3[[#This Row],[Tamanho]]="P",5,
-IF(Tabela3[[#This Row],[Tamanho]]="M",8,
-IF(Tabela3[[#This Row],[Tamanho]]="G",13,
-IF(Tabela3[[#This Row],[Tamanho]]="GG",21,0)))))</f>
+        <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
+IF(Tabela33[[#This Row],[Tamanho]]="P",5,
+IF(Tabela33[[#This Row],[Tamanho]]="M",8,
+IF(Tabela33[[#This Row],[Tamanho]]="G",13,
+IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
       <c r="F36" s="39">
@@ -9971,89 +8924,89 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="62"/>
-      <c r="B37" s="62"/>
-      <c r="C37" s="61"/>
-      <c r="D37" s="61"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="61"/>
-      <c r="G37" s="61"/>
+      <c r="A37" s="71"/>
+      <c r="B37" s="71"/>
+      <c r="C37" s="63"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="63"/>
+      <c r="F37" s="63"/>
+      <c r="G37" s="63"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="62"/>
-      <c r="B38" s="62"/>
-      <c r="C38" s="61"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="61"/>
+      <c r="A38" s="71"/>
+      <c r="B38" s="71"/>
+      <c r="C38" s="63"/>
+      <c r="D38" s="63"/>
+      <c r="E38" s="63"/>
+      <c r="F38" s="63"/>
+      <c r="G38" s="63"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="62"/>
-      <c r="B39" s="62"/>
-      <c r="C39" s="61"/>
-      <c r="D39" s="61"/>
-      <c r="E39" s="61"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="61"/>
+      <c r="A39" s="71"/>
+      <c r="B39" s="71"/>
+      <c r="C39" s="63"/>
+      <c r="D39" s="63"/>
+      <c r="E39" s="63"/>
+      <c r="F39" s="63"/>
+      <c r="G39" s="63"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="62"/>
-      <c r="B40" s="62"/>
-      <c r="C40" s="61"/>
-      <c r="D40" s="61"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
+      <c r="A40" s="71"/>
+      <c r="B40" s="71"/>
+      <c r="C40" s="63"/>
+      <c r="D40" s="63"/>
+      <c r="E40" s="63"/>
+      <c r="F40" s="63"/>
+      <c r="G40" s="63"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="62"/>
-      <c r="B41" s="62"/>
-      <c r="C41" s="61"/>
-      <c r="D41" s="61"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="61"/>
+      <c r="A41" s="71"/>
+      <c r="B41" s="71"/>
+      <c r="C41" s="63"/>
+      <c r="D41" s="63"/>
+      <c r="E41" s="63"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="63"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="62"/>
-      <c r="B42" s="62"/>
-      <c r="C42" s="61"/>
-      <c r="D42" s="61"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="61"/>
+      <c r="A42" s="71"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="63"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="63"/>
+      <c r="G42" s="63"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="62"/>
-      <c r="B43" s="62"/>
-      <c r="C43" s="61"/>
-      <c r="D43" s="61"/>
-      <c r="E43" s="61"/>
-      <c r="F43" s="61"/>
-      <c r="G43" s="61"/>
+      <c r="A43" s="71"/>
+      <c r="B43" s="71"/>
+      <c r="C43" s="63"/>
+      <c r="D43" s="63"/>
+      <c r="E43" s="63"/>
+      <c r="F43" s="63"/>
+      <c r="G43" s="63"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="62"/>
-      <c r="B44" s="62"/>
-      <c r="C44" s="61"/>
-      <c r="D44" s="61"/>
-      <c r="E44" s="61"/>
-      <c r="F44" s="61"/>
-      <c r="G44" s="61"/>
+      <c r="A44" s="71"/>
+      <c r="B44" s="71"/>
+      <c r="C44" s="63"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="63"/>
+      <c r="G44" s="63"/>
     </row>
     <row r="45" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="62"/>
-      <c r="B45" s="62"/>
-      <c r="C45" s="61"/>
-      <c r="D45" s="61"/>
-      <c r="E45" s="61"/>
-      <c r="F45" s="61"/>
-      <c r="G45" s="61"/>
+      <c r="A45" s="71"/>
+      <c r="B45" s="71"/>
+      <c r="C45" s="63"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="63"/>
+      <c r="F45" s="63"/>
+      <c r="G45" s="63"/>
     </row>
     <row r="46" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="62"/>
-      <c r="B46" s="62"/>
+      <c r="A46" s="71"/>
+      <c r="B46" s="71"/>
       <c r="C46" s="30"/>
       <c r="D46" s="12" t="s">
         <v>117</v>
@@ -10061,14 +9014,14 @@
       <c r="E46" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="F46" s="71" t="s">
+      <c r="F46" s="72" t="s">
         <v>116</v>
       </c>
-      <c r="G46" s="72"/>
+      <c r="G46" s="73"/>
     </row>
     <row r="47" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="62"/>
-      <c r="B47" s="62"/>
+      <c r="A47" s="71"/>
+      <c r="B47" s="71"/>
       <c r="C47" s="14" t="s">
         <v>112</v>
       </c>
@@ -10080,15 +9033,15 @@
         <f>SUM(E48:E51)</f>
         <v>201</v>
       </c>
-      <c r="F47" s="55">
+      <c r="F47" s="74">
         <f>D47-E47</f>
         <v>0</v>
       </c>
-      <c r="G47" s="56"/>
+      <c r="G47" s="75"/>
     </row>
     <row r="48" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="62"/>
-      <c r="B48" s="62"/>
+      <c r="A48" s="71"/>
+      <c r="B48" s="71"/>
       <c r="C48" s="14" t="s">
         <v>123</v>
       </c>
@@ -10100,14 +9053,14 @@
         <f>SUM(E10:E11,E14,E24,E25)</f>
         <v>37</v>
       </c>
-      <c r="F48" s="57">
+      <c r="F48" s="59">
         <v>0</v>
       </c>
-      <c r="G48" s="58"/>
+      <c r="G48" s="60"/>
     </row>
     <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="62"/>
-      <c r="B49" s="62"/>
+      <c r="A49" s="71"/>
+      <c r="B49" s="71"/>
       <c r="C49" s="14" t="s">
         <v>120</v>
       </c>
@@ -10119,15 +9072,15 @@
         <f>SUM(E12,E13,E20,E21,E22,E27,E28,E29)</f>
         <v>57</v>
       </c>
-      <c r="F49" s="57">
+      <c r="F49" s="59">
         <f>D49-E49</f>
         <v>0</v>
       </c>
-      <c r="G49" s="58"/>
+      <c r="G49" s="60"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="62"/>
-      <c r="B50" s="62"/>
+      <c r="A50" s="71"/>
+      <c r="B50" s="71"/>
       <c r="C50" s="14" t="s">
         <v>122</v>
       </c>
@@ -10139,15 +9092,15 @@
         <f>SUM(E15,E17,E18,E19,E26,E30,E31,E32)</f>
         <v>63</v>
       </c>
-      <c r="F50" s="57">
+      <c r="F50" s="59">
         <f>D50-E50</f>
         <v>0</v>
       </c>
-      <c r="G50" s="58"/>
+      <c r="G50" s="60"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="62"/>
-      <c r="B51" s="62"/>
+      <c r="A51" s="71"/>
+      <c r="B51" s="71"/>
       <c r="C51" s="14" t="s">
         <v>121</v>
       </c>
@@ -10159,91 +9112,91 @@
         <f>SUM(E16,E23,E34,E35,E36,E33)</f>
         <v>44</v>
       </c>
-      <c r="F51" s="57">
+      <c r="F51" s="59">
         <f>D51-E51</f>
         <v>0</v>
       </c>
-      <c r="G51" s="58"/>
+      <c r="G51" s="60"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="62"/>
-      <c r="B52" s="62"/>
-      <c r="C52" s="69"/>
-      <c r="D52" s="69"/>
-      <c r="E52" s="69"/>
+      <c r="A52" s="71"/>
+      <c r="B52" s="71"/>
+      <c r="C52" s="76"/>
+      <c r="D52" s="76"/>
+      <c r="E52" s="76"/>
       <c r="F52" s="48"/>
       <c r="G52" s="48"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="62"/>
-      <c r="B53" s="62"/>
-      <c r="C53" s="61"/>
-      <c r="D53" s="61"/>
-      <c r="E53" s="61"/>
+      <c r="A53" s="71"/>
+      <c r="B53" s="71"/>
+      <c r="C53" s="63"/>
+      <c r="D53" s="63"/>
+      <c r="E53" s="63"/>
       <c r="F53" s="52"/>
       <c r="G53" s="52"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="62"/>
-      <c r="B54" s="62"/>
-      <c r="C54" s="61"/>
-      <c r="D54" s="61"/>
-      <c r="E54" s="61"/>
+      <c r="A54" s="71"/>
+      <c r="B54" s="71"/>
+      <c r="C54" s="63"/>
+      <c r="D54" s="63"/>
+      <c r="E54" s="63"/>
       <c r="F54" s="52"/>
       <c r="G54" s="52"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="62"/>
-      <c r="B55" s="62"/>
-      <c r="C55" s="61"/>
-      <c r="D55" s="61"/>
-      <c r="E55" s="61"/>
+      <c r="A55" s="71"/>
+      <c r="B55" s="71"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
+      <c r="E55" s="63"/>
       <c r="F55" s="52"/>
       <c r="G55" s="52"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="62"/>
-      <c r="B56" s="62"/>
-      <c r="C56" s="61"/>
-      <c r="D56" s="61"/>
-      <c r="E56" s="61"/>
+      <c r="A56" s="71"/>
+      <c r="B56" s="71"/>
+      <c r="C56" s="63"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="63"/>
       <c r="F56" s="52"/>
       <c r="G56" s="52"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="62"/>
-      <c r="B57" s="62"/>
-      <c r="C57" s="61"/>
-      <c r="D57" s="61"/>
-      <c r="E57" s="61"/>
+      <c r="A57" s="71"/>
+      <c r="B57" s="71"/>
+      <c r="C57" s="63"/>
+      <c r="D57" s="63"/>
+      <c r="E57" s="63"/>
       <c r="F57" s="52"/>
       <c r="G57" s="52"/>
     </row>
     <row r="58" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="62"/>
-      <c r="B58" s="62"/>
-      <c r="C58" s="61"/>
-      <c r="D58" s="61"/>
-      <c r="E58" s="61"/>
+      <c r="A58" s="71"/>
+      <c r="B58" s="71"/>
+      <c r="C58" s="63"/>
+      <c r="D58" s="63"/>
+      <c r="E58" s="63"/>
       <c r="F58" s="52"/>
       <c r="G58" s="52"/>
     </row>
     <row r="59" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="62"/>
-      <c r="B59" s="62"/>
+      <c r="A59" s="71"/>
+      <c r="B59" s="71"/>
       <c r="C59" s="30"/>
       <c r="D59" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="E59" s="61"/>
-      <c r="F59" s="63" t="s">
+      <c r="E59" s="63"/>
+      <c r="F59" s="64" t="s">
         <v>136</v>
       </c>
-      <c r="G59" s="64"/>
+      <c r="G59" s="65"/>
     </row>
     <row r="60" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="62"/>
-      <c r="B60" s="62"/>
+      <c r="A60" s="71"/>
+      <c r="B60" s="71"/>
       <c r="C60" s="14" t="s">
         <v>112</v>
       </c>
@@ -10251,13 +9204,13 @@
         <f>SUM(E10:E36)</f>
         <v>201</v>
       </c>
-      <c r="E60" s="61"/>
-      <c r="F60" s="65"/>
-      <c r="G60" s="66"/>
+      <c r="E60" s="63"/>
+      <c r="F60" s="66"/>
+      <c r="G60" s="67"/>
     </row>
     <row r="61" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="62"/>
-      <c r="B61" s="62"/>
+      <c r="A61" s="71"/>
+      <c r="B61" s="71"/>
       <c r="C61" s="14" t="s">
         <v>123</v>
       </c>
@@ -10265,13 +9218,13 @@
         <f>D60-D48</f>
         <v>164</v>
       </c>
-      <c r="E61" s="61"/>
-      <c r="F61" s="67"/>
-      <c r="G61" s="68"/>
+      <c r="E61" s="63"/>
+      <c r="F61" s="68"/>
+      <c r="G61" s="69"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="62"/>
-      <c r="B62" s="62"/>
+      <c r="A62" s="71"/>
+      <c r="B62" s="71"/>
       <c r="C62" s="14" t="s">
         <v>120</v>
       </c>
@@ -10279,17 +9232,17 @@
         <f>D61-D49</f>
         <v>107</v>
       </c>
-      <c r="E62" s="61"/>
+      <c r="E62" s="63"/>
       <c r="F62" s="49" t="s">
         <v>124</v>
       </c>
       <c r="G62" s="50" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="62"/>
-      <c r="B63" s="62"/>
+      <c r="A63" s="71"/>
+      <c r="B63" s="71"/>
       <c r="C63" s="14" t="s">
         <v>122</v>
       </c>
@@ -10297,18 +9250,18 @@
         <f>D62-E50</f>
         <v>44</v>
       </c>
-      <c r="E63" s="61"/>
+      <c r="E63" s="63"/>
       <c r="F63" s="45" t="s">
         <v>115</v>
       </c>
       <c r="G63" s="43">
         <f>VLOOKUP(G62,C46:G51,3,FALSE)</f>
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="62"/>
-      <c r="B64" s="62"/>
+      <c r="A64" s="71"/>
+      <c r="B64" s="71"/>
       <c r="C64" s="14" t="s">
         <v>121</v>
       </c>
@@ -10316,98 +9269,98 @@
         <f>D51+F50-E51</f>
         <v>0</v>
       </c>
-      <c r="E64" s="61"/>
+      <c r="E64" s="63"/>
       <c r="F64" s="45" t="s">
         <v>117</v>
       </c>
       <c r="G64" s="43">
         <f>VLOOKUP(G62,C46:G51,2,FALSE)</f>
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="62"/>
-      <c r="B65" s="62"/>
-      <c r="C65" s="61"/>
-      <c r="D65" s="61"/>
-      <c r="E65" s="61"/>
-      <c r="F65" s="61"/>
-      <c r="G65" s="61"/>
+      <c r="A65" s="71"/>
+      <c r="B65" s="71"/>
+      <c r="C65" s="63"/>
+      <c r="D65" s="63"/>
+      <c r="E65" s="63"/>
+      <c r="F65" s="63"/>
+      <c r="G65" s="63"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="62"/>
-      <c r="B66" s="62"/>
-      <c r="C66" s="61"/>
-      <c r="D66" s="61"/>
-      <c r="E66" s="61"/>
-      <c r="F66" s="61"/>
-      <c r="G66" s="61"/>
+      <c r="A66" s="71"/>
+      <c r="B66" s="71"/>
+      <c r="C66" s="63"/>
+      <c r="D66" s="63"/>
+      <c r="E66" s="63"/>
+      <c r="F66" s="63"/>
+      <c r="G66" s="63"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="62"/>
-      <c r="B67" s="62"/>
-      <c r="C67" s="61"/>
-      <c r="D67" s="61"/>
-      <c r="E67" s="61"/>
-      <c r="F67" s="61"/>
-      <c r="G67" s="61"/>
+      <c r="A67" s="71"/>
+      <c r="B67" s="71"/>
+      <c r="C67" s="63"/>
+      <c r="D67" s="63"/>
+      <c r="E67" s="63"/>
+      <c r="F67" s="63"/>
+      <c r="G67" s="63"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="62"/>
-      <c r="B68" s="62"/>
-      <c r="C68" s="61"/>
-      <c r="D68" s="61"/>
-      <c r="E68" s="61"/>
-      <c r="F68" s="61"/>
-      <c r="G68" s="61"/>
+      <c r="A68" s="71"/>
+      <c r="B68" s="71"/>
+      <c r="C68" s="63"/>
+      <c r="D68" s="63"/>
+      <c r="E68" s="63"/>
+      <c r="F68" s="63"/>
+      <c r="G68" s="63"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="62"/>
-      <c r="B69" s="62"/>
-      <c r="C69" s="61"/>
-      <c r="D69" s="61"/>
-      <c r="E69" s="61"/>
-      <c r="F69" s="61"/>
-      <c r="G69" s="61"/>
+      <c r="A69" s="71"/>
+      <c r="B69" s="71"/>
+      <c r="C69" s="63"/>
+      <c r="D69" s="63"/>
+      <c r="E69" s="63"/>
+      <c r="F69" s="63"/>
+      <c r="G69" s="63"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B71" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="E59:E64"/>
+    <mergeCell ref="F59:G61"/>
     <mergeCell ref="C65:G69"/>
+    <mergeCell ref="A1:G8"/>
     <mergeCell ref="A37:B69"/>
-    <mergeCell ref="F59:G61"/>
-    <mergeCell ref="C52:E58"/>
-    <mergeCell ref="A1:G8"/>
-    <mergeCell ref="E59:E64"/>
     <mergeCell ref="C37:G45"/>
-    <mergeCell ref="F51:G51"/>
     <mergeCell ref="F46:G46"/>
     <mergeCell ref="F47:G47"/>
     <mergeCell ref="F48:G48"/>
     <mergeCell ref="F49:G49"/>
     <mergeCell ref="F50:G50"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C52:E58"/>
   </mergeCells>
   <conditionalFormatting sqref="A10:D36 F10:G36">
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>#REF!="Sim"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>#REF!=1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="8">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Insira uma descrição do item nesta coluna" sqref="B9" xr:uid="{3E0CDA96-62DA-4783-91B0-EAD60F8F8A14}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Insira o preço unitário de cada item nesta coluna" sqref="C9" xr:uid="{72914D10-8A28-40C0-9FE1-EE37279638B5}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Insira a quantidade em estoque de cada item nesta coluna" sqref="D9" xr:uid="{6399A917-1012-4753-A266-23A4E693DD3B}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Esse é um valor de estoque column._x000a__x000a_O valor de estoque de cada item é automaticamente calculado nesta coluna." sqref="E9" xr:uid="{6DA33C9F-E7EB-4EBB-BE05-900589138049}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Insira o nível de estoque de cada item nesta coluna" sqref="F9" xr:uid="{8FAF9DD4-C30E-4934-9B5E-7C6B02F23E75}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Insira quantos dias faltam para realizar nova encomenda de cada item nesta coluna" sqref="G9" xr:uid="{CBC61B02-1456-47C8-A9D5-E64F7EEDE2A3}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Insira o nome do item nesta coluna" sqref="A9" xr:uid="{4AEACA9D-41A6-4BE8-BD8B-AE83A899E5EE}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G62" xr:uid="{259A99CB-B18F-4E5F-9C4F-7B0E2CA304A4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G62" xr:uid="{48A427D4-E98B-4464-8932-C27C4F25EBEB}">
       <formula1>$C$48:$C$51</formula1>
     </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Insira o nome do item nesta coluna" sqref="A9" xr:uid="{F68BE7A7-AEC5-4C2F-ADBE-A75174293901}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Insira quantos dias faltam para realizar nova encomenda de cada item nesta coluna" sqref="G9" xr:uid="{7B9C7BF5-5261-46AB-AB3D-17E3CF322AFA}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Insira o nível de estoque de cada item nesta coluna" sqref="F9" xr:uid="{C4A02465-4662-40A3-BD6B-75874F44CCD7}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Esse é um valor de estoque column._x000a__x000a_O valor de estoque de cada item é automaticamente calculado nesta coluna." sqref="E9" xr:uid="{8D368F22-17EA-4D58-A7DC-08CCB36CCD50}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Insira a quantidade em estoque de cada item nesta coluna" sqref="D9" xr:uid="{FFB33C16-B029-4D4D-9A01-AC6077AC35F6}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Insira o preço unitário de cada item nesta coluna" sqref="C9" xr:uid="{650C0D00-0C81-483A-B470-9B922899F74C}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Insira uma descrição do item nesta coluna" sqref="B9" xr:uid="{D1F626B7-F27B-4554-BB65-289A9B6DD78C}"/>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
@@ -10418,51 +9371,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <xsd:import namespace="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
-    <xsd:import namespace="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A729CFA7192B0F4AA60BE2DF65F4BC74" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c88fc727e37bcbeb6d3a40296a022323">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="8497f9ae-9c71-438c-b553-1e6fe8b1acb0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="77a4e7418373acf0c30a5fd0050b4a86" ns3:_="">
+    <xsd:import namespace="8497f9ae-9c71-438c-b553-1e6fe8b1acb0"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:Status" minOccurs="0"/>
-                <xsd:element ref="ns2:Image" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:ImageTagsTaxHTField" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:Background" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDocTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSystemTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -10470,173 +9392,33 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8497f9ae-9c71-438c-b553-1e6fe8b1acb0" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="20" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties" ma:readOnly="false">
+    <xsd:element name="MediaServiceDateTaken" ma:index="8" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="21" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="Status" ma:index="2" nillable="true" ma:displayName="Status" ma:default="Not started" ma:format="Dropdown" ma:internalName="Status" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Choice">
-          <xsd:enumeration value="Not started"/>
-          <xsd:enumeration value="In Progress"/>
-          <xsd:enumeration value="Completed"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Image" ma:index="3" nillable="true" ma:displayName="Image" ma:format="Image" ma:internalName="Image" ma:readOnly="false">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:URL">
-            <xsd:sequence>
-              <xsd:element name="Url" type="dms:ValidUrl" minOccurs="0" nillable="true"/>
-              <xsd:element name="Description" type="xsd:string" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="10" nillable="true" ma:displayName="MediaServiceOCR" ma:hidden="true" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="_activity" ma:index="12" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="11" nillable="true" ma:displayName="MediaServiceAutoTags" ma:hidden="true" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="12" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="16" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="17" nillable="true" ma:displayName="KeyPoints" ma:hidden="true" ma:internalName="MediaServiceKeyPoints" ma:readOnly="false">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="18" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="ImageTagsTaxHTField" ma:index="25" nillable="true" ma:taxonomy="true" ma:internalName="ImageTagsTaxHTField" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="e385fb40-52d4-4fae-9c5b-3e8ff8a5878e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="26" nillable="true" ma:displayName="Location" ma:hidden="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="27" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Background" ma:index="28" nillable="true" ma:displayName="Background" ma:default="0" ma:format="Dropdown" ma:internalName="Background">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Boolean"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="29" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDocTags" ma:index="30" nillable="true" ma:displayName="MediaServiceDocTags" ma:hidden="true" ma:internalName="MediaServiceDocTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="31" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSystemTags" ma:index="32" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="16c05727-aa75-4e4a-9b5f-8a80a1165891" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="14" nillable="true" ma:displayName="Shared With" ma:hidden="true" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="15" nillable="true" ma:displayName="Shared With Details" ma:hidden="true" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="230e9df3-be65-4c73-a93b-d1236ebd677e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{3f6bfcbc-3db3-4ae6-bd76-326f0798ad28}" ma:internalName="TaxCatchAll" ma:readOnly="false" ma:showField="CatchAllData" ma:web="16c05727-aa75-4e4a-9b5f-8a80a1165891">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -10648,8 +9430,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="1" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -10738,45 +9520,31 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+    <_activity xmlns="8497f9ae-9c71-438c-b553-1e6fe8b1acb0" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A83B3E02-9081-4283-A1B6-3FADACFC660C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84764C01-755B-4501-9893-DE1587D322EE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A3FC760-E629-409A-86BC-CC3C163C0ACB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="8497f9ae-9c71-438c-b553-1e6fe8b1acb0"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -10787,21 +9555,26 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A83B3E02-9081-4283-A1B6-3FADACFC660C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E347ADB8-BE75-4F14-ADF9-E64D4A3FD476}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8497f9ae-9c71-438c-b553-1e6fe8b1acb0"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Documentos/Planilha de Requisitos - WHIS{KEY}.xlsx
+++ b/Documentos/Planilha de Requisitos - WHIS{KEY}.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6622D939-2C9F-4AE8-80F5-E739A8873DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD0BFDC0-DE2F-44C3-AB0B-F9DBE0FA9943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requisitos Projeto" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="139">
   <si>
     <t>Planilha de requisitos</t>
   </si>
@@ -451,6 +451,9 @@
   </si>
   <si>
     <t>SPRINT</t>
+  </si>
+  <si>
+    <t>Pontos FIBONACCI</t>
   </si>
 </sst>
 </file>
@@ -464,7 +467,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -613,14 +616,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FF000000"/>
-      <name val="Univers"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Univers"/>
@@ -679,15 +674,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color theme="8" tint="-0.249977111117893"/>
-      <name val="Univers"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="45">
+  <fills count="47">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -939,8 +927,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="24">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -1211,7 +1211,69 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color theme="8"/>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1265,7 +1327,7 @@
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1283,13 +1345,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1307,25 +1369,22 @@
     <xf numFmtId="0" fontId="2" fillId="38" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1348,45 +1407,33 @@
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="166" fontId="24" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="23" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="166" fontId="24" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="23" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
@@ -1403,24 +1450,60 @@
     <xf numFmtId="0" fontId="0" fillId="38" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="42" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="45" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="46" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1456,10 +1539,10 @@
     <xf numFmtId="0" fontId="0" fillId="43" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="35" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2242,26 +2325,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:defRPr sz="4000" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="lt1">
-                    <a:lumMod val="95000"/>
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:effectLst>
-                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                    <a:prstClr val="black">
-                      <a:alpha val="40000"/>
-                    </a:prstClr>
-                  </a:outerShdw>
-                </a:effectLst>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="pt-BR"/>
+              <a:rPr lang="pt-BR" sz="4000"/>
               <a:t>Gráfico de Burndown</a:t>
             </a:r>
           </a:p>
@@ -2280,19 +2356,12 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+            <a:defRPr sz="4000" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
+                  <a:lumMod val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:effectLst>
-                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="40000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
@@ -2309,10 +2378,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="3.8896369184796942E-2"/>
-          <c:y val="0.10285657108998883"/>
-          <c:w val="0.93039807981758804"/>
-          <c:h val="0.71375699704749107"/>
+          <c:x val="6.1118022103384989E-2"/>
+          <c:y val="4.8134829354119946E-2"/>
+          <c:w val="0.87476457392722906"/>
+          <c:h val="0.75383352922937141"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -2322,29 +2391,21 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>'Requisitos Projeto'!$E$61</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Planejado</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Planejado</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="34925" cap="rnd">
+            <a:ln w="22225" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
             <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
             </a:effectLst>
           </c:spPr>
           <c:marker>
@@ -2352,11 +2413,11 @@
           </c:marker>
           <c:dLbls>
             <c:dLbl>
-              <c:idx val="0"/>
+              <c:idx val="1"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-5.6005406700528004E-2"/>
-                  <c:y val="1.2967568353693979E-2"/>
+                  <c:x val="3.2318063079776006E-2"/>
+                  <c:y val="-7.7990467194023638E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:dLblPos val="r"/>
@@ -2369,16 +2430,16 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000008-8360-4B32-9D96-76E4CA36749F}"/>
+                  <c16:uniqueId val="{00000005-DC15-4B31-B926-878A63C30504}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
-              <c:idx val="1"/>
+              <c:idx val="2"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-1.9418222616270513E-2"/>
-                  <c:y val="2.8209234745635518E-2"/>
+                  <c:x val="-8.2111079065158146E-2"/>
+                  <c:y val="4.4724579784971047E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:dLblPos val="r"/>
@@ -2391,115 +2452,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000006-8360-4B32-9D96-76E4CA36749F}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="3.1442612530688248E-3"/>
-                  <c:y val="-3.5328329968891216E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                  <a:noAutofit/>
-                </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="lt1">
-                          <a:lumMod val="85000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="pt-BR"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="r"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout>
-                    <c:manualLayout>
-                      <c:w val="3.9762643359697605E-2"/>
-                      <c:h val="4.7691494421093931E-2"/>
-                    </c:manualLayout>
-                  </c15:layout>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000002-8360-4B32-9D96-76E4CA36749F}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="3"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                  <a:noAutofit/>
-                </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="lt1">
-                          <a:lumMod val="85000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="pt-BR"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout>
-                    <c:manualLayout>
-                      <c:w val="5.4186719640408026E-2"/>
-                      <c:h val="7.6781009477298906E-2"/>
-                    </c:manualLayout>
-                  </c15:layout>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000004-8360-4B32-9D96-76E4CA36749F}"/>
+                  <c16:uniqueId val="{00000003-DC15-4B31-B926-878A63C30504}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2517,10 +2470,10 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="6000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="lt1">
-                        <a:lumMod val="85000"/>
+                        <a:lumMod val="75000"/>
                       </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
@@ -2547,10 +2500,10 @@
                     <a:ln w="9525">
                       <a:solidFill>
                         <a:schemeClr val="lt1">
-                          <a:lumMod val="95000"/>
-                          <a:alpha val="54000"/>
+                          <a:lumMod val="50000"/>
                         </a:schemeClr>
                       </a:solidFill>
+                      <a:round/>
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
@@ -2560,7 +2513,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Requisitos Projeto'!$D$62:$D$65</c:f>
+              <c:f>'Requisitos Projeto'!$O$5:$O$8</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -2580,7 +2533,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Requisitos Projeto'!$E$62:$E$65</c:f>
+              <c:f>'Requisitos Projeto'!$Q$5:$Q$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2588,13 +2541,13 @@
                   <c:v>378</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>93</c:v>
+                  <c:v>252</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>201</c:v>
+                  <c:v>126</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>84</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2602,7 +2555,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8360-4B32-9D96-76E4CA36749F}"/>
+              <c16:uniqueId val="{00000000-DC15-4B31-B926-878A63C30504}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2610,29 +2563,21 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:strRef>
-              <c:f>'Requisitos Projeto'!$F$61</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Entregue</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Entregue</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="34925" cap="rnd">
+            <a:ln w="22225" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent4"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
             <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent4">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
             </a:effectLst>
           </c:spPr>
           <c:marker>
@@ -2640,11 +2585,11 @@
           </c:marker>
           <c:dLbls>
             <c:dLbl>
-              <c:idx val="0"/>
+              <c:idx val="1"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-1.1911041484677804E-2"/>
-                  <c:y val="-4.3693159782819471E-2"/>
+                  <c:x val="-7.8430180140072428E-2"/>
+                  <c:y val="0.1390503248509147"/>
                 </c:manualLayout>
               </c:layout>
               <c:dLblPos val="r"/>
@@ -2657,16 +2602,16 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000007-8360-4B32-9D96-76E4CA36749F}"/>
+                  <c16:uniqueId val="{00000004-DC15-4B31-B926-878A63C30504}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
-              <c:idx val="1"/>
+              <c:idx val="2"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-4.6051036521593222E-4"/>
-                  <c:y val="-5.0753548637536679E-2"/>
+                  <c:x val="4.2043530439198167E-2"/>
+                  <c:y val="-7.6158899328665541E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:dLblPos val="r"/>
@@ -2679,29 +2624,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-8360-4B32-9D96-76E4CA36749F}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-1.9871978545066088E-2"/>
-                  <c:y val="5.5767722693619064E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:dLblPos val="r"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000003-8360-4B32-9D96-76E4CA36749F}"/>
+                  <c16:uniqueId val="{00000006-DC15-4B31-B926-878A63C30504}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2719,10 +2642,10 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="6000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="lt1">
-                        <a:lumMod val="85000"/>
+                        <a:lumMod val="75000"/>
                       </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
@@ -2749,10 +2672,10 @@
                     <a:ln w="9525">
                       <a:solidFill>
                         <a:schemeClr val="lt1">
-                          <a:lumMod val="95000"/>
-                          <a:alpha val="54000"/>
+                          <a:lumMod val="50000"/>
                         </a:schemeClr>
                       </a:solidFill>
+                      <a:round/>
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
@@ -2762,7 +2685,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Requisitos Projeto'!$D$62:$D$65</c:f>
+              <c:f>'Requisitos Projeto'!$O$5:$O$8</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -2782,18 +2705,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Requisitos Projeto'!$F$62:$F$65</c:f>
+              <c:f>'Requisitos Projeto'!$R$5:$R$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>294</c:v>
+                  <c:v>378</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>93</c:v>
+                  <c:v>252</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>201</c:v>
+                  <c:v>113</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2804,7 +2727,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8360-4B32-9D96-76E4CA36749F}"/>
+              <c16:uniqueId val="{00000002-DC15-4B31-B926-878A63C30504}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2818,133 +2741,16 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1484819359"/>
-        <c:axId val="1484814559"/>
+        <c:axId val="665695296"/>
+        <c:axId val="665697216"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1484819359"/>
+        <c:axId val="665695296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:lumMod val="95000"/>
-                <a:alpha val="10000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1484814559"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1484814559"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                  <a:alpha val="10000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="lt1">
-                        <a:lumMod val="85000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="pt-BR"/>
-                  <a:t>TAM#</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="85000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="pt-BR"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2961,10 +2767,10 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="4000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
+                    <a:lumMod val="75000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -2975,7 +2781,76 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1484819359"/>
+        <c:crossAx val="665697216"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="665697216"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="665695296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2988,15 +2863,15 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="r"/>
       <c:layout>
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.37796263101462502"/>
-          <c:y val="0.87286591999961427"/>
-          <c:w val="0.20704229479104944"/>
-          <c:h val="0.11641689024283657"/>
+          <c:x val="0.31393496540046806"/>
+          <c:y val="0.90305842989926377"/>
+          <c:w val="0.38181051209657213"/>
+          <c:h val="9.0531082571982779E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -3012,10 +2887,10 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="4800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="lt1">
-                  <a:lumMod val="85000"/>
+                  <a:lumMod val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -3039,28 +2914,20 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="85000"/>
-            <a:lumOff val="15000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="circle">
-        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
-    <a:ln>
-      <a:noFill/>
+    <a:solidFill>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
     </a:ln>
     <a:effectLst/>
   </c:spPr>
@@ -3570,17 +3437,17 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="233">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="236">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -3588,20 +3455,9 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="10000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea>
@@ -3612,28 +3468,23 @@
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="65000"/>
-              <a:lumOff val="35000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="85000"/>
-              <a:lumOff val="15000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-        </a:path>
-        <a:tileRect/>
-      </a:gradFill>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -3641,7 +3492,7 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -3651,14 +3502,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
       </a:solidFill>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -3667,72 +3521,131 @@
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="3"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="34925" cap="rnd">
+      <a:ln w="22225" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:round/>
       </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="3">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="3"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -3749,15 +3662,15 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -3769,22 +3682,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -3793,17 +3706,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="dash"/>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -3812,13 +3724,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3830,7 +3742,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
@@ -3838,16 +3750,27 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="10000"/>
-          </a:schemeClr>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
@@ -3857,16 +3780,30 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="5000"/>
-          </a:schemeClr>
-        </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -3875,17 +3812,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="dash"/>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -3894,16 +3830,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -3913,7 +3849,7 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -3923,7 +3859,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D>
@@ -3931,7 +3867,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -3940,20 +3876,9 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -3961,14 +3886,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3981,18 +3905,10 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1">
-        <a:lumMod val="95000"/>
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:defRPr>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -4001,12 +3917,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="25400" cap="rnd">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
         </a:solidFill>
       </a:ln>
     </cs:spPr>
@@ -4017,7 +3935,7 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -4027,19 +3945,21 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -4049,7 +3969,7 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -4059,7 +3979,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -4563,42 +4483,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>803935</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>336294</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>9095150</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>241096</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Gráfico 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7479607-4C07-4CD9-8CE0-A5D29F5CBB4F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -4626,7 +4510,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -4650,54 +4534,40 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1081037</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>80188</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>71718</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>119063</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3746820</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>317415</xdr:rowOff>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>119062</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>270963</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagem 1">
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76F56776-1C1A-43B4-B775-8CE66AD28E89}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1503CBDE-3A07-DA03-CC16-82CE03B3775E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1366787" y="23606938"/>
-          <a:ext cx="2665783" cy="1380227"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -5095,96 +4965,159 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I748"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AT748"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.75" style="3" customWidth="1"/>
-    <col min="2" max="2" width="75.75" style="5" customWidth="1"/>
-    <col min="3" max="3" width="138.375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="21.125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="16.75" style="6" customWidth="1"/>
-    <col min="6" max="6" width="18.75" style="6" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="75.69921875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="138.3984375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="21.09765625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="16.69921875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="18.69921875" style="6" customWidth="1"/>
     <col min="7" max="7" width="22" style="6" customWidth="1"/>
     <col min="8" max="8" width="24" style="6" customWidth="1"/>
-    <col min="9" max="9" width="4.125" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="8.625" style="3"/>
+    <col min="9" max="9" width="4.09765625" style="3" customWidth="1"/>
+    <col min="10" max="13" width="8.59765625" style="3"/>
+    <col min="14" max="14" width="5.09765625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="8.59765625" style="3"/>
+    <col min="16" max="16" width="20.59765625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="12" style="3" customWidth="1"/>
+    <col min="18" max="18" width="11.59765625" style="3" customWidth="1"/>
+    <col min="19" max="16384" width="8.59765625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22"/>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="22"/>
-    </row>
-    <row r="2" spans="1:9" ht="110.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23"/>
-      <c r="B2" s="57" t="s">
+    <row r="1" spans="1:46" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="21"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="53"/>
+      <c r="X1" s="53"/>
+      <c r="Y1" s="53"/>
+      <c r="Z1" s="53"/>
+      <c r="AA1" s="53"/>
+      <c r="AB1" s="53"/>
+      <c r="AC1" s="53"/>
+      <c r="AD1" s="53"/>
+      <c r="AE1" s="53"/>
+      <c r="AF1" s="53"/>
+      <c r="AG1" s="53"/>
+      <c r="AH1" s="53"/>
+      <c r="AI1" s="53"/>
+      <c r="AJ1" s="53"/>
+      <c r="AK1" s="53"/>
+      <c r="AL1" s="53"/>
+      <c r="AM1" s="53"/>
+      <c r="AN1" s="53"/>
+      <c r="AO1" s="53"/>
+      <c r="AP1" s="53"/>
+      <c r="AQ1" s="53"/>
+      <c r="AR1" s="53"/>
+      <c r="AS1" s="53"/>
+      <c r="AT1" s="54"/>
+    </row>
+    <row r="2" spans="1:46" ht="110.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="22"/>
+      <c r="B2" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="23"/>
-    </row>
-    <row r="3" spans="1:9" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="23"/>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="23"/>
-    </row>
-    <row r="4" spans="1:9" s="4" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24"/>
-      <c r="B4" s="34" t="s">
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="55"/>
+      <c r="AT2" s="56"/>
+    </row>
+    <row r="3" spans="1:46" ht="45.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="22"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="55"/>
+      <c r="AT3" s="56"/>
+    </row>
+    <row r="4" spans="1:46" s="4" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="23"/>
+      <c r="B4" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="G4" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="34" t="s">
+      <c r="H4" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="I4" s="24"/>
-    </row>
-    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="23"/>
-      <c r="B5" s="16" t="s">
+      <c r="I4" s="23"/>
+      <c r="J4" s="57"/>
+      <c r="O4" s="63"/>
+      <c r="P4" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q4" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="R4" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="S4" s="70" t="s">
+        <v>116</v>
+      </c>
+      <c r="T4" s="71"/>
+      <c r="AT4" s="58"/>
+    </row>
+    <row r="5" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="22"/>
+      <c r="B5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -5192,16 +5125,37 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>3</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="15">
         <v>2</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="23"/>
-    </row>
-    <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="23"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="55"/>
+      <c r="O5" s="64" t="s">
+        <v>112</v>
+      </c>
+      <c r="P5" s="62">
+        <f>SUM(F5:F56)</f>
+        <v>378</v>
+      </c>
+      <c r="Q5" s="62">
+        <f>SUM(Inventory_List_Table[Tam('#)])</f>
+        <v>378</v>
+      </c>
+      <c r="R5" s="62">
+        <v>378</v>
+      </c>
+      <c r="S5" s="68">
+        <f>Q5-R5</f>
+        <v>0</v>
+      </c>
+      <c r="T5" s="69"/>
+      <c r="AT5" s="56"/>
+    </row>
+    <row r="6" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="22"/>
       <c r="B6" s="7" t="s">
         <v>12</v>
       </c>
@@ -5228,23 +5182,43 @@
       <c r="H6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="23"/>
-    </row>
-    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="23"/>
-      <c r="B7" s="16" t="s">
+      <c r="I6" s="22"/>
+      <c r="J6" s="55"/>
+      <c r="O6" s="64" t="s">
+        <v>113</v>
+      </c>
+      <c r="P6" s="11">
+        <f>SUM(F5:F19)</f>
+        <v>93</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>252</v>
+      </c>
+      <c r="R6" s="11">
+        <f>Q6</f>
+        <v>252</v>
+      </c>
+      <c r="S6" s="68">
+        <v>0</v>
+      </c>
+      <c r="T6" s="69"/>
+      <c r="AT6" s="56"/>
+    </row>
+    <row r="7" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="22"/>
+      <c r="B7" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -5252,16 +5226,36 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="15">
         <v>1</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="23"/>
-    </row>
-    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="23"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="55"/>
+      <c r="O7" s="64" t="s">
+        <v>47</v>
+      </c>
+      <c r="P7" s="11">
+        <f>SUM(F20:F46)</f>
+        <v>201</v>
+      </c>
+      <c r="Q7" s="11">
+        <v>126</v>
+      </c>
+      <c r="R7" s="11">
+        <f>Q7-S7</f>
+        <v>113</v>
+      </c>
+      <c r="S7" s="65">
+        <v>13</v>
+      </c>
+      <c r="T7" s="65"/>
+      <c r="AT7" s="56"/>
+    </row>
+    <row r="8" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="22"/>
       <c r="B8" s="7" t="s">
         <v>17</v>
       </c>
@@ -5288,23 +5282,42 @@
       <c r="H8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="23"/>
-    </row>
-    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="23"/>
-      <c r="B9" s="16" t="s">
+      <c r="I8" s="22"/>
+      <c r="J8" s="55"/>
+      <c r="O8" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="P8" s="11">
+        <f>SUM(F47:F56)</f>
+        <v>84</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="65">
+        <v>0</v>
+      </c>
+      <c r="T8" s="65"/>
+      <c r="AT8" s="56"/>
+    </row>
+    <row r="9" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="22"/>
+      <c r="B9" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -5312,16 +5325,18 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>13</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="15">
         <v>3</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="23"/>
-    </row>
-    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="23"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="55"/>
+      <c r="AT9" s="56"/>
+    </row>
+    <row r="10" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="22"/>
       <c r="B10" s="7" t="s">
         <v>22</v>
       </c>
@@ -5348,23 +5363,25 @@
       <c r="H10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I10" s="23"/>
-    </row>
-    <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="23"/>
-      <c r="B11" s="16" t="s">
+      <c r="I10" s="22"/>
+      <c r="J10" s="55"/>
+      <c r="AT10" s="56"/>
+    </row>
+    <row r="11" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="22"/>
+      <c r="B11" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -5372,16 +5389,18 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>3</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="15">
         <v>2</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="I11" s="23"/>
-    </row>
-    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="23"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="55"/>
+      <c r="AT11" s="56"/>
+    </row>
+    <row r="12" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="22"/>
       <c r="B12" s="7" t="s">
         <v>27</v>
       </c>
@@ -5408,23 +5427,25 @@
       <c r="H12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="23"/>
-    </row>
-    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="23"/>
-      <c r="B13" s="16" t="s">
+      <c r="I12" s="22"/>
+      <c r="J12" s="55"/>
+      <c r="AT12" s="56"/>
+    </row>
+    <row r="13" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="22"/>
+      <c r="B13" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -5432,16 +5453,18 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="15">
         <v>2</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="H13" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="I13" s="23"/>
-    </row>
-    <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="23"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="55"/>
+      <c r="AT13" s="56"/>
+    </row>
+    <row r="14" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="22"/>
       <c r="B14" s="7" t="s">
         <v>32</v>
       </c>
@@ -5468,23 +5491,25 @@
       <c r="H14" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="23"/>
-    </row>
-    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="23"/>
-      <c r="B15" s="16" t="s">
+      <c r="I14" s="22"/>
+      <c r="J14" s="55"/>
+      <c r="AT14" s="56"/>
+    </row>
+    <row r="15" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="22"/>
+      <c r="B15" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -5492,16 +5517,18 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="15">
         <v>3</v>
       </c>
-      <c r="H15" s="16" t="s">
+      <c r="H15" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="I15" s="23"/>
-    </row>
-    <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="23"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="55"/>
+      <c r="AT15" s="56"/>
+    </row>
+    <row r="16" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="22"/>
       <c r="B16" s="7" t="s">
         <v>37</v>
       </c>
@@ -5528,23 +5555,25 @@
       <c r="H16" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I16" s="23"/>
-    </row>
-    <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="23"/>
-      <c r="B17" s="16" t="s">
+      <c r="I16" s="22"/>
+      <c r="J16" s="55"/>
+      <c r="AT16" s="56"/>
+    </row>
+    <row r="17" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="22"/>
+      <c r="B17" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -5552,16 +5581,18 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="15">
         <v>3</v>
       </c>
-      <c r="H17" s="16" t="s">
+      <c r="H17" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="I17" s="23"/>
-    </row>
-    <row r="18" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="23"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="55"/>
+      <c r="AT17" s="56"/>
+    </row>
+    <row r="18" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="22"/>
       <c r="B18" s="7" t="s">
         <v>41</v>
       </c>
@@ -5588,23 +5619,25 @@
       <c r="H18" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I18" s="23"/>
-    </row>
-    <row r="19" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="23"/>
-      <c r="B19" s="16" t="s">
+      <c r="I18" s="22"/>
+      <c r="J18" s="55"/>
+      <c r="AT18" s="56"/>
+    </row>
+    <row r="19" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="22"/>
+      <c r="B19" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -5612,29 +5645,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>3</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="15">
         <v>1</v>
       </c>
-      <c r="H19" s="16" t="s">
+      <c r="H19" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="I19" s="23"/>
-    </row>
-    <row r="20" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="23"/>
-      <c r="B20" s="54" t="s">
+      <c r="I19" s="22"/>
+      <c r="J19" s="55"/>
+      <c r="AT19" s="56"/>
+    </row>
+    <row r="20" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="22"/>
+      <c r="B20" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="54" t="s">
+      <c r="C20" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="55" t="s">
+      <c r="D20" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="54" t="s">
+      <c r="E20" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F20" s="56">
+      <c r="F20" s="50">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -5642,29 +5677,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>13</v>
       </c>
-      <c r="G20" s="54">
+      <c r="G20" s="48">
         <v>1</v>
       </c>
-      <c r="H20" s="54" t="s">
+      <c r="H20" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="I20" s="23"/>
-    </row>
-    <row r="21" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="23"/>
-      <c r="B21" s="16" t="s">
+      <c r="I20" s="22"/>
+      <c r="J20" s="55"/>
+      <c r="AT20" s="56"/>
+    </row>
+    <row r="21" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="22"/>
+      <c r="B21" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -5672,29 +5709,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="15">
         <v>1</v>
       </c>
-      <c r="H21" s="16" t="s">
+      <c r="H21" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="I21" s="23"/>
-    </row>
-    <row r="22" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="23"/>
-      <c r="B22" s="19" t="s">
+      <c r="I21" s="22"/>
+      <c r="J21" s="55"/>
+      <c r="AT21" s="56"/>
+    </row>
+    <row r="22" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="22"/>
+      <c r="B22" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="20">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -5702,29 +5741,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="18">
         <v>2</v>
       </c>
-      <c r="H22" s="19" t="s">
+      <c r="H22" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I22" s="23"/>
-    </row>
-    <row r="23" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="23"/>
-      <c r="B23" s="16" t="s">
+      <c r="I22" s="22"/>
+      <c r="J22" s="55"/>
+      <c r="AT22" s="56"/>
+    </row>
+    <row r="23" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="22"/>
+      <c r="B23" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="E23" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -5732,29 +5773,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>13</v>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="15">
         <v>2</v>
       </c>
-      <c r="H23" s="16" t="s">
+      <c r="H23" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="I23" s="23"/>
-    </row>
-    <row r="24" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="23"/>
-      <c r="B24" s="19" t="s">
+      <c r="I23" s="22"/>
+      <c r="J23" s="55"/>
+      <c r="AT23" s="56"/>
+    </row>
+    <row r="24" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="22"/>
+      <c r="B24" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="D24" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="21">
+      <c r="F24" s="20">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -5762,29 +5805,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>3</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="18">
         <v>1</v>
       </c>
-      <c r="H24" s="19" t="s">
+      <c r="H24" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I24" s="23"/>
-    </row>
-    <row r="25" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="23"/>
-      <c r="B25" s="16" t="s">
+      <c r="I24" s="22"/>
+      <c r="J24" s="55"/>
+      <c r="AT24" s="56"/>
+    </row>
+    <row r="25" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="22"/>
+      <c r="B25" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="E25" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -5792,29 +5837,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="15">
         <v>2</v>
       </c>
-      <c r="H25" s="16" t="s">
+      <c r="H25" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="I25" s="23"/>
-    </row>
-    <row r="26" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="23"/>
-      <c r="B26" s="19" t="s">
+      <c r="I25" s="22"/>
+      <c r="J25" s="55"/>
+      <c r="AT25" s="56"/>
+    </row>
+    <row r="26" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="22"/>
+      <c r="B26" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="E26" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F26" s="21">
+      <c r="F26" s="20">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -5822,29 +5869,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="18">
         <v>1</v>
       </c>
-      <c r="H26" s="19" t="s">
+      <c r="H26" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I26" s="23"/>
-    </row>
-    <row r="27" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="23"/>
-      <c r="B27" s="36" t="s">
+      <c r="I26" s="22"/>
+      <c r="J26" s="55"/>
+      <c r="AT26" s="56"/>
+    </row>
+    <row r="27" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="22"/>
+      <c r="B27" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="C27" s="36" t="s">
+      <c r="C27" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="D27" s="37" t="s">
+      <c r="D27" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="36" t="s">
+      <c r="E27" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="F27" s="38">
+      <c r="F27" s="33">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -5852,29 +5901,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="G27" s="36">
+      <c r="G27" s="31">
         <v>3</v>
       </c>
-      <c r="H27" s="36" t="s">
+      <c r="H27" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="I27" s="23"/>
-    </row>
-    <row r="28" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="23"/>
-      <c r="B28" s="19" t="s">
+      <c r="I27" s="22"/>
+      <c r="J27" s="55"/>
+      <c r="AT27" s="56"/>
+    </row>
+    <row r="28" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="22"/>
+      <c r="B28" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="E28" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F28" s="21">
+      <c r="F28" s="20">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -5882,29 +5933,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="18">
         <v>1</v>
       </c>
-      <c r="H28" s="19" t="s">
+      <c r="H28" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I28" s="23"/>
-    </row>
-    <row r="29" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="23"/>
-      <c r="B29" s="16" t="s">
+      <c r="I28" s="22"/>
+      <c r="J28" s="55"/>
+      <c r="AT28" s="56"/>
+    </row>
+    <row r="29" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="22"/>
+      <c r="B29" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="E29" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F29" s="18">
+      <c r="F29" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -5912,29 +5965,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>13</v>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="15">
         <v>3</v>
       </c>
-      <c r="H29" s="16" t="s">
+      <c r="H29" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="I29" s="23"/>
-    </row>
-    <row r="30" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="23"/>
-      <c r="B30" s="19" t="s">
+      <c r="I29" s="22"/>
+      <c r="J29" s="55"/>
+      <c r="AT29" s="56"/>
+    </row>
+    <row r="30" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="22"/>
+      <c r="B30" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="D30" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="E30" s="19" t="s">
+      <c r="E30" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F30" s="21">
+      <c r="F30" s="20">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -5942,29 +5997,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="G30" s="19">
+      <c r="G30" s="18">
         <v>2</v>
       </c>
-      <c r="H30" s="19" t="s">
+      <c r="H30" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I30" s="23"/>
-    </row>
-    <row r="31" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="23"/>
-      <c r="B31" s="16" t="s">
+      <c r="I30" s="22"/>
+      <c r="J30" s="55"/>
+      <c r="AT30" s="56"/>
+    </row>
+    <row r="31" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="22"/>
+      <c r="B31" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F31" s="18">
+      <c r="F31" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -5972,29 +6029,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="15">
         <v>2</v>
       </c>
-      <c r="H31" s="16" t="s">
+      <c r="H31" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="I31" s="23"/>
-    </row>
-    <row r="32" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="23"/>
-      <c r="B32" s="19" t="s">
+      <c r="I31" s="22"/>
+      <c r="J31" s="55"/>
+      <c r="AT31" s="56"/>
+    </row>
+    <row r="32" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="22"/>
+      <c r="B32" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D32" s="20" t="s">
+      <c r="D32" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="E32" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F32" s="21">
+      <c r="F32" s="20">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6002,29 +6061,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="18">
         <v>2</v>
       </c>
-      <c r="H32" s="19" t="s">
+      <c r="H32" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I32" s="23"/>
-    </row>
-    <row r="33" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="23"/>
-      <c r="B33" s="16" t="s">
+      <c r="I32" s="22"/>
+      <c r="J32" s="55"/>
+      <c r="AT32" s="56"/>
+    </row>
+    <row r="33" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="22"/>
+      <c r="B33" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E33" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F33" s="18">
+      <c r="F33" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6032,29 +6093,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="15">
         <v>3</v>
       </c>
-      <c r="H33" s="16" t="s">
+      <c r="H33" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="I33" s="23"/>
-    </row>
-    <row r="34" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="23"/>
-      <c r="B34" s="19" t="s">
+      <c r="I33" s="22"/>
+      <c r="J33" s="55"/>
+      <c r="AT33" s="56"/>
+    </row>
+    <row r="34" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="22"/>
+      <c r="B34" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="20" t="s">
+      <c r="D34" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="E34" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F34" s="21">
+      <c r="F34" s="20">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6062,29 +6125,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="G34" s="19">
+      <c r="G34" s="18">
         <v>1</v>
       </c>
-      <c r="H34" s="19" t="s">
+      <c r="H34" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I34" s="23"/>
-    </row>
-    <row r="35" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="23"/>
-      <c r="B35" s="16" t="s">
+      <c r="I34" s="22"/>
+      <c r="J34" s="55"/>
+      <c r="AT34" s="56"/>
+    </row>
+    <row r="35" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="22"/>
+      <c r="B35" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E35" s="16" t="s">
+      <c r="E35" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F35" s="18">
+      <c r="F35" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6092,29 +6157,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="15">
         <v>1</v>
       </c>
-      <c r="H35" s="16" t="s">
+      <c r="H35" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="I35" s="23"/>
-    </row>
-    <row r="36" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="23"/>
-      <c r="B36" s="19" t="s">
+      <c r="I35" s="22"/>
+      <c r="J35" s="55"/>
+      <c r="AT35" s="56"/>
+    </row>
+    <row r="36" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="22"/>
+      <c r="B36" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="19" t="s">
+      <c r="C36" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D36" s="20" t="s">
+      <c r="D36" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="19" t="s">
+      <c r="E36" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F36" s="21">
+      <c r="F36" s="20">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6122,29 +6189,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="G36" s="19">
+      <c r="G36" s="18">
         <v>3</v>
       </c>
-      <c r="H36" s="19" t="s">
+      <c r="H36" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I36" s="23"/>
-    </row>
-    <row r="37" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="23"/>
-      <c r="B37" s="16" t="s">
+      <c r="I36" s="22"/>
+      <c r="J36" s="55"/>
+      <c r="AT36" s="56"/>
+    </row>
+    <row r="37" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="22"/>
+      <c r="B37" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="16" t="s">
+      <c r="E37" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F37" s="18">
+      <c r="F37" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6152,29 +6221,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="15">
         <v>1</v>
       </c>
-      <c r="H37" s="16" t="s">
+      <c r="H37" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="I37" s="23"/>
-    </row>
-    <row r="38" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="23"/>
-      <c r="B38" s="19" t="s">
+      <c r="I37" s="22"/>
+      <c r="J37" s="55"/>
+      <c r="AT37" s="56"/>
+    </row>
+    <row r="38" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="22"/>
+      <c r="B38" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D38" s="20" t="s">
+      <c r="D38" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="E38" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F38" s="21">
+      <c r="F38" s="20">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6182,29 +6253,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="G38" s="19">
+      <c r="G38" s="18">
         <v>2</v>
       </c>
-      <c r="H38" s="19" t="s">
+      <c r="H38" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I38" s="23"/>
-    </row>
-    <row r="39" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="23"/>
-      <c r="B39" s="16" t="s">
+      <c r="I38" s="22"/>
+      <c r="J38" s="55"/>
+      <c r="AT38" s="56"/>
+    </row>
+    <row r="39" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="22"/>
+      <c r="B39" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="E39" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F39" s="18">
+      <c r="F39" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6212,29 +6285,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="G39" s="16">
+      <c r="G39" s="15">
         <v>3</v>
       </c>
-      <c r="H39" s="16" t="s">
+      <c r="H39" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="I39" s="23"/>
-    </row>
-    <row r="40" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="23"/>
-      <c r="B40" s="19" t="s">
+      <c r="I39" s="22"/>
+      <c r="J39" s="55"/>
+      <c r="AT39" s="56"/>
+    </row>
+    <row r="40" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="22"/>
+      <c r="B40" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="C40" s="19" t="s">
+      <c r="C40" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D40" s="20" t="s">
+      <c r="D40" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="E40" s="19" t="s">
+      <c r="E40" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F40" s="21">
+      <c r="F40" s="20">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6242,29 +6317,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="G40" s="19">
+      <c r="G40" s="18">
         <v>3</v>
       </c>
-      <c r="H40" s="19" t="s">
+      <c r="H40" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I40" s="23"/>
-    </row>
-    <row r="41" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="23"/>
-      <c r="B41" s="16" t="s">
+      <c r="I40" s="22"/>
+      <c r="J40" s="55"/>
+      <c r="AT40" s="56"/>
+    </row>
+    <row r="41" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="22"/>
+      <c r="B41" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E41" s="16" t="s">
+      <c r="E41" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F41" s="18">
+      <c r="F41" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6272,29 +6349,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>3</v>
       </c>
-      <c r="G41" s="16">
+      <c r="G41" s="15">
         <v>2</v>
       </c>
-      <c r="H41" s="16" t="s">
+      <c r="H41" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="I41" s="23"/>
-    </row>
-    <row r="42" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="23"/>
-      <c r="B42" s="19" t="s">
+      <c r="I41" s="22"/>
+      <c r="J41" s="55"/>
+      <c r="AT41" s="56"/>
+    </row>
+    <row r="42" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="22"/>
+      <c r="B42" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C42" s="19" t="s">
+      <c r="C42" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D42" s="20" t="s">
+      <c r="D42" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="E42" s="19" t="s">
+      <c r="E42" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="F42" s="21">
+      <c r="F42" s="20">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6302,29 +6381,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>13</v>
       </c>
-      <c r="G42" s="19">
+      <c r="G42" s="18">
         <v>3</v>
       </c>
-      <c r="H42" s="19" t="s">
+      <c r="H42" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I42" s="23"/>
-    </row>
-    <row r="43" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="23"/>
-      <c r="B43" s="16" t="s">
+      <c r="I42" s="22"/>
+      <c r="J42" s="55"/>
+      <c r="AT42" s="56"/>
+    </row>
+    <row r="43" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="22"/>
+      <c r="B43" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E43" s="16" t="s">
+      <c r="E43" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F43" s="18">
+      <c r="F43" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6332,29 +6413,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>13</v>
       </c>
-      <c r="G43" s="16">
+      <c r="G43" s="15">
         <v>3</v>
       </c>
-      <c r="H43" s="16" t="s">
+      <c r="H43" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="I43" s="23"/>
-    </row>
-    <row r="44" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="23"/>
-      <c r="B44" s="19" t="s">
+      <c r="I43" s="22"/>
+      <c r="J43" s="55"/>
+      <c r="AT43" s="56"/>
+    </row>
+    <row r="44" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="22"/>
+      <c r="B44" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="C44" s="19" t="s">
+      <c r="C44" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D44" s="20" t="s">
+      <c r="D44" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E44" s="19" t="s">
+      <c r="E44" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F44" s="21">
+      <c r="F44" s="20">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6362,29 +6445,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="G44" s="19">
+      <c r="G44" s="18">
         <v>3</v>
       </c>
-      <c r="H44" s="19" t="s">
+      <c r="H44" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I44" s="23"/>
-    </row>
-    <row r="45" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="23"/>
-      <c r="B45" s="16" t="s">
+      <c r="I44" s="22"/>
+      <c r="J44" s="55"/>
+      <c r="AT44" s="56"/>
+    </row>
+    <row r="45" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="22"/>
+      <c r="B45" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="C45" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D45" s="17" t="s">
+      <c r="D45" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E45" s="16" t="s">
+      <c r="E45" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F45" s="18">
+      <c r="F45" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6392,29 +6477,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="G45" s="16">
+      <c r="G45" s="15">
         <v>2</v>
       </c>
-      <c r="H45" s="16" t="s">
+      <c r="H45" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="I45" s="23"/>
-    </row>
-    <row r="46" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="23"/>
-      <c r="B46" s="19" t="s">
+      <c r="I45" s="22"/>
+      <c r="J45" s="55"/>
+      <c r="AT45" s="56"/>
+    </row>
+    <row r="46" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="22"/>
+      <c r="B46" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C46" s="19" t="s">
+      <c r="C46" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="D46" s="20" t="s">
+      <c r="D46" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E46" s="19" t="s">
+      <c r="E46" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F46" s="21">
+      <c r="F46" s="20">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6422,29 +6509,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="G46" s="19">
+      <c r="G46" s="18">
         <v>2</v>
       </c>
-      <c r="H46" s="19" t="s">
+      <c r="H46" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I46" s="23"/>
-    </row>
-    <row r="47" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="23"/>
-      <c r="B47" s="16" t="s">
+      <c r="I46" s="22"/>
+      <c r="J46" s="55"/>
+      <c r="AT46" s="56"/>
+    </row>
+    <row r="47" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="22"/>
+      <c r="B47" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E47" s="16" t="s">
+      <c r="E47" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F47" s="18">
+      <c r="F47" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6452,29 +6541,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>3</v>
       </c>
-      <c r="G47" s="16">
+      <c r="G47" s="15">
         <v>3</v>
       </c>
-      <c r="H47" s="16" t="s">
+      <c r="H47" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="I47" s="23"/>
-    </row>
-    <row r="48" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="23"/>
-      <c r="B48" s="19" t="s">
+      <c r="I47" s="22"/>
+      <c r="J47" s="55"/>
+      <c r="AT47" s="56"/>
+    </row>
+    <row r="48" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="22"/>
+      <c r="B48" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="C48" s="19" t="s">
+      <c r="C48" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D48" s="20" t="s">
+      <c r="D48" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E48" s="19" t="s">
+      <c r="E48" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F48" s="21">
+      <c r="F48" s="20">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6482,29 +6573,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="G48" s="19">
+      <c r="G48" s="18">
         <v>3</v>
       </c>
-      <c r="H48" s="19" t="s">
+      <c r="H48" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="I48" s="23"/>
-    </row>
-    <row r="49" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="23"/>
-      <c r="B49" s="16" t="s">
+      <c r="I48" s="22"/>
+      <c r="J48" s="55"/>
+      <c r="AT48" s="56"/>
+    </row>
+    <row r="49" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="22"/>
+      <c r="B49" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="D49" s="17" t="s">
+      <c r="D49" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E49" s="16" t="s">
+      <c r="E49" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F49" s="18">
+      <c r="F49" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6512,29 +6605,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="G49" s="16">
+      <c r="G49" s="15">
         <v>3</v>
       </c>
-      <c r="H49" s="16" t="s">
+      <c r="H49" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="I49" s="23"/>
-    </row>
-    <row r="50" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="23"/>
-      <c r="B50" s="19" t="s">
+      <c r="I49" s="22"/>
+      <c r="J49" s="55"/>
+      <c r="AT49" s="56"/>
+    </row>
+    <row r="50" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="22"/>
+      <c r="B50" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="19" t="s">
+      <c r="C50" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="D50" s="20" t="s">
+      <c r="D50" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="E50" s="19" t="s">
+      <c r="E50" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="F50" s="21">
+      <c r="F50" s="20">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6542,29 +6637,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>13</v>
       </c>
-      <c r="G50" s="19">
+      <c r="G50" s="18">
         <v>3</v>
       </c>
-      <c r="H50" s="19" t="s">
+      <c r="H50" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="I50" s="23"/>
-    </row>
-    <row r="51" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="23"/>
-      <c r="B51" s="16" t="s">
+      <c r="I50" s="22"/>
+      <c r="J50" s="55"/>
+      <c r="AT50" s="56"/>
+    </row>
+    <row r="51" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="22"/>
+      <c r="B51" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C51" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D51" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E51" s="16" t="s">
+      <c r="E51" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F51" s="18">
+      <c r="F51" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6572,29 +6669,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="G51" s="16">
+      <c r="G51" s="15">
         <v>3</v>
       </c>
-      <c r="H51" s="16" t="s">
+      <c r="H51" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="I51" s="23"/>
-    </row>
-    <row r="52" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="23"/>
-      <c r="B52" s="19" t="s">
+      <c r="I51" s="22"/>
+      <c r="J51" s="55"/>
+      <c r="AT51" s="56"/>
+    </row>
+    <row r="52" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="22"/>
+      <c r="B52" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="C52" s="19" t="s">
+      <c r="C52" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="D52" s="20" t="s">
+      <c r="D52" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="E52" s="19" t="s">
+      <c r="E52" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F52" s="21">
+      <c r="F52" s="20">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6602,29 +6701,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="G52" s="19">
+      <c r="G52" s="18">
         <v>3</v>
       </c>
-      <c r="H52" s="19" t="s">
+      <c r="H52" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="I52" s="23"/>
-    </row>
-    <row r="53" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="23"/>
-      <c r="B53" s="16" t="s">
+      <c r="I52" s="22"/>
+      <c r="J52" s="55"/>
+      <c r="AT52" s="56"/>
+    </row>
+    <row r="53" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="22"/>
+      <c r="B53" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="D53" s="17" t="s">
+      <c r="D53" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E53" s="16" t="s">
+      <c r="E53" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F53" s="18">
+      <c r="F53" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6632,29 +6733,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="G53" s="16">
+      <c r="G53" s="15">
         <v>3</v>
       </c>
-      <c r="H53" s="16" t="s">
+      <c r="H53" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="I53" s="23"/>
-    </row>
-    <row r="54" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="23"/>
-      <c r="B54" s="19" t="s">
+      <c r="I53" s="22"/>
+      <c r="J53" s="55"/>
+      <c r="AT53" s="56"/>
+    </row>
+    <row r="54" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="22"/>
+      <c r="B54" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="C54" s="19" t="s">
+      <c r="C54" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="D54" s="20" t="s">
+      <c r="D54" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="E54" s="19" t="s">
+      <c r="E54" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F54" s="21">
+      <c r="F54" s="20">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6662,29 +6765,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="G54" s="19">
+      <c r="G54" s="18">
         <v>2</v>
       </c>
-      <c r="H54" s="19" t="s">
+      <c r="H54" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="I54" s="23"/>
-    </row>
-    <row r="55" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="23"/>
-      <c r="B55" s="16" t="s">
+      <c r="I54" s="22"/>
+      <c r="J54" s="55"/>
+      <c r="AT54" s="56"/>
+    </row>
+    <row r="55" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="22"/>
+      <c r="B55" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C55" s="16" t="s">
+      <c r="C55" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="D55" s="17" t="s">
+      <c r="D55" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E55" s="16" t="s">
+      <c r="E55" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F55" s="18">
+      <c r="F55" s="17">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6692,29 +6797,31 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>13</v>
       </c>
-      <c r="G55" s="16">
+      <c r="G55" s="15">
         <v>3</v>
       </c>
-      <c r="H55" s="16" t="s">
+      <c r="H55" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="I55" s="23"/>
-    </row>
-    <row r="56" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="23"/>
-      <c r="B56" s="19" t="s">
+      <c r="I55" s="22"/>
+      <c r="J55" s="55"/>
+      <c r="AT55" s="56"/>
+    </row>
+    <row r="56" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="22"/>
+      <c r="B56" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="C56" s="19" t="s">
+      <c r="C56" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="D56" s="20" t="s">
+      <c r="D56" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="E56" s="19" t="s">
+      <c r="E56" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="F56" s="21">
+      <c r="F56" s="20">
         <f>IF(Inventory_List_Table[[#This Row],[Tamanho]]="PP",3,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="P",5,
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="M",8,
@@ -6722,477 +6829,160 @@
 IF(Inventory_List_Table[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>13</v>
       </c>
-      <c r="G56" s="19">
+      <c r="G56" s="18">
         <v>2</v>
       </c>
-      <c r="H56" s="19" t="s">
+      <c r="H56" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="I56" s="23"/>
-    </row>
-    <row r="57" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="23"/>
-      <c r="B57" s="27"/>
-      <c r="C57" s="27"/>
-      <c r="D57" s="28"/>
-      <c r="E57" s="28"/>
-      <c r="F57" s="28"/>
-      <c r="G57" s="28"/>
-      <c r="H57" s="28"/>
-      <c r="I57" s="23"/>
-    </row>
-    <row r="58" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="23"/>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="30"/>
-      <c r="I58" s="23"/>
-    </row>
-    <row r="59" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="23"/>
-      <c r="B59" s="29"/>
-      <c r="C59" s="29"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="30"/>
-      <c r="F59" s="30"/>
-      <c r="G59" s="30"/>
-      <c r="H59" s="30"/>
-      <c r="I59" s="23"/>
-    </row>
-    <row r="60" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="23"/>
-      <c r="B60" s="29"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="30"/>
-      <c r="F60" s="30"/>
-      <c r="G60" s="30"/>
-      <c r="H60" s="30"/>
-      <c r="I60" s="23"/>
-    </row>
-    <row r="61" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="23"/>
-      <c r="B61" s="29"/>
-      <c r="C61" s="31"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="F61" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="G61" s="61" t="s">
-        <v>116</v>
-      </c>
-      <c r="H61" s="62"/>
-      <c r="I61" s="23"/>
-    </row>
-    <row r="62" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="23"/>
-      <c r="B62" s="29"/>
-      <c r="C62" s="29"/>
-      <c r="D62" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="E62" s="15">
-        <f>SUM(Inventory_List_Table[Tam('#)])</f>
-        <v>378</v>
-      </c>
-      <c r="F62" s="15">
-        <f>SUM(Inventory_List_Table[Tam('#)])-E65</f>
-        <v>294</v>
-      </c>
-      <c r="G62" s="59">
-        <f>E62-F62</f>
-        <v>84</v>
-      </c>
-      <c r="H62" s="60"/>
-      <c r="I62" s="23"/>
-    </row>
-    <row r="63" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="23"/>
-      <c r="B63" s="29"/>
-      <c r="C63" s="29"/>
-      <c r="D63" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E63" s="13">
-        <f>SUM(F5:F19)</f>
-        <v>93</v>
-      </c>
-      <c r="F63" s="11">
-        <f>SUM(F5:F19)</f>
-        <v>93</v>
-      </c>
-      <c r="G63" s="59">
-        <v>0</v>
-      </c>
-      <c r="H63" s="60"/>
-      <c r="I63" s="23"/>
-    </row>
-    <row r="64" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="23"/>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="E64" s="13">
-        <f>SUM(F20:F46)</f>
-        <v>201</v>
-      </c>
-      <c r="F64" s="11">
-        <f>SUM(F40,F46,F45,F44,F42,F41,F20:F39,F43)</f>
-        <v>201</v>
-      </c>
-      <c r="G64" s="59">
-        <f>E64-F64</f>
-        <v>0</v>
-      </c>
-      <c r="H64" s="60"/>
-      <c r="I64" s="23"/>
-    </row>
-    <row r="65" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="23"/>
-      <c r="B65" s="29"/>
-      <c r="C65" s="29"/>
-      <c r="D65" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E65" s="13">
-        <f>SUM(F47:F56)</f>
-        <v>84</v>
-      </c>
-      <c r="F65" s="11">
-        <v>0</v>
-      </c>
-      <c r="G65" s="59">
-        <f>E65-F65</f>
-        <v>84</v>
-      </c>
-      <c r="H65" s="60"/>
-      <c r="I65" s="23"/>
-    </row>
-    <row r="66" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="23"/>
-      <c r="B66" s="29"/>
-      <c r="C66" s="32"/>
-      <c r="D66" s="30"/>
-      <c r="E66" s="30"/>
-      <c r="F66" s="30"/>
-      <c r="G66" s="30"/>
-      <c r="H66" s="30"/>
-      <c r="I66" s="23"/>
-    </row>
-    <row r="67" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="23"/>
-      <c r="B67" s="29"/>
-      <c r="C67" s="33"/>
-      <c r="D67" s="30"/>
-      <c r="E67" s="30"/>
-      <c r="F67" s="30"/>
-      <c r="G67" s="30"/>
-      <c r="H67" s="30"/>
-      <c r="I67" s="23"/>
-    </row>
-    <row r="68" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="23"/>
-      <c r="B68" s="29"/>
-      <c r="C68" s="33"/>
-      <c r="D68" s="30"/>
-      <c r="E68" s="30"/>
-      <c r="F68" s="30"/>
-      <c r="G68" s="30"/>
-      <c r="H68" s="30"/>
-      <c r="I68" s="23"/>
-    </row>
-    <row r="69" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="23"/>
-      <c r="B69" s="29"/>
-      <c r="C69" s="29"/>
-      <c r="D69" s="30"/>
-      <c r="E69" s="30"/>
-      <c r="F69" s="30"/>
-      <c r="G69" s="30"/>
-      <c r="H69" s="30"/>
-      <c r="I69" s="23"/>
-    </row>
-    <row r="70" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="23"/>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="23"/>
-    </row>
-    <row r="71" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="23"/>
-      <c r="B71" s="29"/>
-      <c r="C71" s="29"/>
-      <c r="D71" s="30"/>
-      <c r="E71" s="30"/>
-      <c r="F71" s="30"/>
-      <c r="G71" s="30"/>
-      <c r="H71" s="30"/>
-      <c r="I71" s="23"/>
-    </row>
-    <row r="72" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="23"/>
-      <c r="B72" s="29"/>
-      <c r="C72" s="29"/>
-      <c r="D72" s="30"/>
-      <c r="E72" s="30"/>
-      <c r="F72" s="30"/>
-      <c r="G72" s="30"/>
-      <c r="H72" s="30"/>
-      <c r="I72" s="23"/>
-    </row>
-    <row r="73" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="23"/>
-      <c r="B73" s="29"/>
-      <c r="C73" s="29"/>
-      <c r="D73" s="30"/>
-      <c r="E73" s="30"/>
-      <c r="F73" s="30"/>
-      <c r="G73" s="30"/>
-      <c r="H73" s="30"/>
-      <c r="I73" s="23"/>
-    </row>
-    <row r="74" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="23"/>
-      <c r="B74" s="29"/>
-      <c r="C74" s="29"/>
-      <c r="D74" s="30"/>
-      <c r="E74" s="30"/>
-      <c r="F74" s="30"/>
-      <c r="G74" s="30"/>
-      <c r="H74" s="30"/>
-      <c r="I74" s="23"/>
-    </row>
-    <row r="75" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="23"/>
-      <c r="B75" s="29"/>
-      <c r="C75" s="29"/>
-      <c r="D75" s="30"/>
-      <c r="E75" s="30"/>
-      <c r="F75" s="30"/>
-      <c r="G75" s="30"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="23"/>
-    </row>
-    <row r="76" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="23"/>
-      <c r="B76" s="29"/>
-      <c r="C76" s="29"/>
-      <c r="D76" s="30"/>
-      <c r="E76" s="30"/>
-      <c r="F76" s="30"/>
-      <c r="G76" s="30"/>
-      <c r="H76" s="30"/>
-      <c r="I76" s="23"/>
-    </row>
-    <row r="77" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="23"/>
-      <c r="B77" s="29"/>
-      <c r="C77" s="29"/>
-      <c r="D77" s="30"/>
-      <c r="E77" s="30"/>
-      <c r="F77" s="30"/>
-      <c r="G77" s="30"/>
-      <c r="H77" s="30"/>
-      <c r="I77" s="23"/>
-    </row>
-    <row r="78" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="23"/>
-      <c r="B78" s="29"/>
-      <c r="C78" s="29"/>
-      <c r="D78" s="30"/>
-      <c r="E78" s="30"/>
-      <c r="F78" s="30"/>
-      <c r="G78" s="30"/>
-      <c r="H78" s="30"/>
-      <c r="I78" s="23"/>
-    </row>
-    <row r="79" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="23"/>
-      <c r="B79" s="29"/>
-      <c r="C79" s="29"/>
-      <c r="D79" s="30"/>
-      <c r="E79" s="30"/>
-      <c r="F79" s="30"/>
-      <c r="G79" s="30"/>
-      <c r="H79" s="30"/>
-      <c r="I79" s="23"/>
-    </row>
-    <row r="80" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="23"/>
-      <c r="B80" s="29"/>
-      <c r="C80" s="29"/>
-      <c r="D80" s="30"/>
-      <c r="E80" s="30"/>
-      <c r="F80" s="30"/>
-      <c r="G80" s="30"/>
-      <c r="H80" s="30"/>
-      <c r="I80" s="23"/>
-    </row>
-    <row r="81" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="23"/>
-      <c r="B81" s="29"/>
-      <c r="C81" s="29"/>
-      <c r="D81" s="30"/>
-      <c r="E81" s="30"/>
-      <c r="F81" s="30"/>
-      <c r="G81" s="30"/>
-      <c r="H81" s="30"/>
-      <c r="I81" s="23"/>
-    </row>
-    <row r="82" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="23"/>
-      <c r="B82" s="29"/>
-      <c r="C82" s="29"/>
-      <c r="D82" s="30"/>
-      <c r="E82" s="30"/>
-      <c r="F82" s="30"/>
-      <c r="G82" s="30"/>
-      <c r="H82" s="30"/>
-      <c r="I82" s="23"/>
-    </row>
-    <row r="83" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="23"/>
-      <c r="B83" s="53"/>
-      <c r="C83" s="53"/>
-      <c r="D83" s="53"/>
-      <c r="E83" s="53"/>
-      <c r="F83" s="53"/>
-      <c r="G83" s="53"/>
-      <c r="H83" s="53"/>
-      <c r="I83" s="53"/>
-    </row>
-    <row r="84" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-    </row>
-    <row r="85" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
-    </row>
-    <row r="86" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
-    </row>
-    <row r="87" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="3"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
-    </row>
-    <row r="88" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="3"/>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3"/>
-      <c r="E88" s="3"/>
-      <c r="F88" s="3"/>
-      <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
-    </row>
-    <row r="89" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="3"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
-      <c r="F89" s="3"/>
-      <c r="G89" s="3"/>
-      <c r="H89" s="3"/>
-    </row>
-    <row r="90" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="3"/>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3"/>
-      <c r="E90" s="3"/>
-      <c r="F90" s="3"/>
-      <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
-    </row>
-    <row r="91" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="3"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
-    </row>
-    <row r="92" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="3"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
-    </row>
-    <row r="93" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="3"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
-      <c r="F93" s="3"/>
-      <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
-    </row>
-    <row r="94" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="3"/>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3"/>
-      <c r="E94" s="3"/>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3"/>
-      <c r="H94" s="3"/>
-    </row>
-    <row r="95" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="3"/>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
-    </row>
-    <row r="96" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B96" s="3"/>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3"/>
-      <c r="E96" s="3"/>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3"/>
-      <c r="H96" s="3"/>
-    </row>
-    <row r="97" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I56" s="22"/>
+      <c r="J56" s="55"/>
+      <c r="AT56" s="56"/>
+    </row>
+    <row r="57" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="22"/>
+      <c r="B57" s="26"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="27"/>
+      <c r="E57" s="27"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="27"/>
+      <c r="I57" s="22"/>
+      <c r="J57" s="59"/>
+      <c r="K57" s="51"/>
+      <c r="L57" s="51"/>
+      <c r="M57" s="51"/>
+      <c r="N57" s="51"/>
+      <c r="O57" s="51"/>
+      <c r="P57" s="51"/>
+      <c r="Q57" s="51"/>
+      <c r="R57" s="51"/>
+      <c r="S57" s="51"/>
+      <c r="T57" s="51"/>
+      <c r="U57" s="51"/>
+      <c r="V57" s="51"/>
+      <c r="W57" s="51"/>
+      <c r="X57" s="51"/>
+      <c r="Y57" s="51"/>
+      <c r="Z57" s="51"/>
+      <c r="AA57" s="51"/>
+      <c r="AB57" s="51"/>
+      <c r="AC57" s="51"/>
+      <c r="AD57" s="51"/>
+      <c r="AE57" s="51"/>
+      <c r="AF57" s="51"/>
+      <c r="AG57" s="51"/>
+      <c r="AH57" s="51"/>
+      <c r="AI57" s="51"/>
+      <c r="AJ57" s="51"/>
+      <c r="AK57" s="51"/>
+      <c r="AL57" s="51"/>
+      <c r="AM57" s="51"/>
+      <c r="AN57" s="51"/>
+      <c r="AO57" s="51"/>
+      <c r="AP57" s="51"/>
+      <c r="AQ57" s="51"/>
+      <c r="AR57" s="51"/>
+      <c r="AS57" s="51"/>
+      <c r="AT57" s="60"/>
+    </row>
+    <row r="58" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+    </row>
+    <row r="59" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+    </row>
+    <row r="61" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+    </row>
+    <row r="62" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+    </row>
+    <row r="63" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+    </row>
+    <row r="64" spans="1:46" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+    </row>
+    <row r="65" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="68" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="69" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="70" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="71" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="72" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="73" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="74" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="76" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="77" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="78" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="80" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="81" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="82" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="83" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="84" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="85" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="86" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="87" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="88" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="91" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="92" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="93" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="94" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="95" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="96" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="97" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
@@ -7201,7 +6991,7 @@
       <c r="G97" s="3"/>
       <c r="H97" s="3"/>
     </row>
-    <row r="98" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
@@ -7210,7 +7000,7 @@
       <c r="G98" s="3"/>
       <c r="H98" s="3"/>
     </row>
-    <row r="99" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -7218,7 +7008,7 @@
       <c r="G99" s="3"/>
       <c r="H99" s="3"/>
     </row>
-    <row r="100" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
@@ -7227,7 +7017,7 @@
       <c r="G100" s="3"/>
       <c r="H100" s="3"/>
     </row>
-    <row r="101" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
@@ -7236,7 +7026,7 @@
       <c r="G101" s="3"/>
       <c r="H101" s="3"/>
     </row>
-    <row r="102" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
@@ -7245,7 +7035,7 @@
       <c r="G102" s="3"/>
       <c r="H102" s="3"/>
     </row>
-    <row r="103" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
@@ -7254,7 +7044,7 @@
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
     </row>
-    <row r="104" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
@@ -7263,7 +7053,7 @@
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
     </row>
-    <row r="105" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
@@ -7272,7 +7062,7 @@
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
     </row>
-    <row r="106" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
@@ -7281,7 +7071,7 @@
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
     </row>
-    <row r="107" spans="2:8" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
@@ -7290,7 +7080,7 @@
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
     </row>
-    <row r="108" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
@@ -7299,7 +7089,7 @@
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
     </row>
-    <row r="109" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
@@ -7308,7 +7098,7 @@
       <c r="G109" s="3"/>
       <c r="H109" s="3"/>
     </row>
-    <row r="110" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
@@ -7317,7 +7107,7 @@
       <c r="G110" s="3"/>
       <c r="H110" s="3"/>
     </row>
-    <row r="111" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
@@ -7326,7 +7116,7 @@
       <c r="G111" s="3"/>
       <c r="H111" s="3"/>
     </row>
-    <row r="112" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
@@ -7335,631 +7125,631 @@
       <c r="G112" s="3"/>
       <c r="H112" s="3"/>
     </row>
-    <row r="113" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="114" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="115" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="116" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="117" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="118" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="119" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="120" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="121" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="122" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="123" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="124" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="125" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="126" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="127" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="128" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="129" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="130" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="131" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="132" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="133" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="134" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="135" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="136" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="137" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="138" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="139" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="140" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="141" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="142" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="143" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="144" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="145" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="146" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="147" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="148" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="149" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="150" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="151" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="152" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="153" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="154" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="155" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="156" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="157" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="158" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="159" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="160" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="161" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="162" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="163" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="164" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="165" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="166" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="167" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="168" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="169" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="170" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="171" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="172" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="174" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="182" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="183" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="184" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="187" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="188" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="190" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="191" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="192" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="193" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="194" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="195" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="196" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="197" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="198" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="199" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="200" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="201" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="202" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="203" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="204" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="205" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="206" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="207" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="208" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="209" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="210" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="211" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="212" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="213" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="214" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="215" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="216" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="217" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="218" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="219" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="220" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="221" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="222" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="223" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="224" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="225" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="226" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="227" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="228" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="229" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="230" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="231" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="232" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="233" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="234" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="235" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="236" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="237" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="238" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="239" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="240" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="241" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="242" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="243" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="244" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="245" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="246" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="247" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="248" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="249" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="250" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="251" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="252" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="253" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="254" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="255" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="256" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="257" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="258" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="259" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="260" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="261" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="262" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="263" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="264" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="265" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="266" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="267" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="268" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="269" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="270" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="271" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="272" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="273" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="274" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="275" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="276" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="277" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="278" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="279" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="280" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="281" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="282" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="283" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="284" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="285" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="286" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="287" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="288" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="289" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="290" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="291" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="292" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="293" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="294" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="295" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="296" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="297" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="298" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="299" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="300" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="301" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="302" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="303" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="304" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="305" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="306" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="307" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="308" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="309" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="310" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="311" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="312" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="313" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="314" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="315" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="316" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="317" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="318" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="319" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="320" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="321" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="322" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="323" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="324" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="325" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="326" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="327" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="328" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="329" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="330" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="331" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="332" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="333" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="334" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="335" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="336" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="337" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="338" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="339" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="340" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="341" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="342" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="343" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="344" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="345" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="346" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="347" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="348" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="349" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="350" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="351" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="352" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="353" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="354" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="355" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="356" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="357" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="358" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="359" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="360" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="361" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="362" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="363" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="364" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="365" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="366" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="367" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="368" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="369" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="370" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="371" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="372" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="373" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="374" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="375" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="376" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="377" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="378" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="379" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="380" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="381" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="382" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="383" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="384" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="385" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="386" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="387" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="388" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="389" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="390" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="391" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="392" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="393" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="394" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="395" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="396" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="397" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="398" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="399" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="400" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="401" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="402" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="403" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="404" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="405" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="406" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="407" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="408" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="409" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="410" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="411" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="412" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="413" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="414" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="415" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="416" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="417" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="418" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="419" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="420" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="421" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="422" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="423" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="424" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="425" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="426" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="427" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="428" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="429" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="430" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="431" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="432" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="433" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="434" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="435" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="436" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="437" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="438" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="439" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="440" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="441" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="442" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="443" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="444" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="445" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="446" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="447" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="448" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="449" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="450" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="451" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="452" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="453" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="454" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="455" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="456" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="457" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="458" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="459" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="460" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="461" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="462" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="463" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="464" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="465" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="466" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="467" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="468" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="469" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="470" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="471" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="472" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="473" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="474" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="475" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="476" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="477" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="478" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="479" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="480" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="481" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="482" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="483" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="484" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="485" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="486" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="487" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="488" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="489" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="490" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="491" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="492" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="493" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="494" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="495" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="496" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="497" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="498" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="499" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="500" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="501" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="502" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="503" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="504" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="505" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="506" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="507" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="508" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="509" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="510" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="511" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="512" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="513" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="514" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="515" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="516" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="517" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="518" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="519" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="520" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="521" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="522" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="523" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="524" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="525" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="526" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="527" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="528" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="529" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="530" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="531" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="532" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="533" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="534" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="535" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="536" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="537" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="538" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="539" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="540" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="541" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="542" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="543" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="544" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="545" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="546" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="547" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="548" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="549" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="550" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="551" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="552" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="553" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="554" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="555" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="556" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="557" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="558" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="559" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="560" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="561" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="562" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="563" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="564" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="565" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="566" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="567" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="568" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="569" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="570" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="571" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="572" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="573" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="574" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="575" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="576" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="577" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="578" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="579" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="580" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="581" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="582" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="583" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="584" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="585" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="586" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="587" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="588" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="589" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="590" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="591" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="592" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="593" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="594" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="595" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="596" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="597" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="598" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="599" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="600" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="601" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="602" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="603" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="604" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="605" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="606" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="607" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="608" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="609" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="610" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="611" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="612" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="613" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="614" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="615" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="616" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="617" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="618" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="619" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="620" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="621" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="622" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="623" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="624" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="625" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="626" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="627" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="628" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="629" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="630" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="631" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="632" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="633" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="634" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="635" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="636" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="637" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="638" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="639" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="640" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="641" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="642" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="643" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="644" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="645" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="646" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="647" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="648" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="649" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="650" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="651" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="652" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="653" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="654" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="655" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="656" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="657" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="658" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="659" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="660" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="661" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="662" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="663" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="664" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="665" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="666" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="667" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="668" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="669" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="670" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="671" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="672" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="673" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="674" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="675" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="676" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="677" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="678" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="679" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="680" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="681" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="682" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="683" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="684" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="685" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="686" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="687" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="688" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="689" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="690" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="691" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="692" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="693" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="694" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="695" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="696" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="697" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="698" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="699" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="700" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="701" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="702" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="703" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="704" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="705" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="706" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="707" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="708" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="709" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="710" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="711" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="712" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="713" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="714" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="715" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="716" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="717" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="718" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="719" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="720" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="721" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="722" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="723" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="724" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="725" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="726" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="727" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="728" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="729" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="730" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="731" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="732" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="733" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="734" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="735" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="736" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="737" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B737" s="3"/>
       <c r="C737" s="3"/>
       <c r="D737" s="3"/>
@@ -7968,7 +7758,7 @@
       <c r="G737" s="3"/>
       <c r="H737" s="3"/>
     </row>
-    <row r="738" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B738" s="3"/>
       <c r="C738" s="3"/>
       <c r="D738" s="3"/>
@@ -7977,7 +7767,7 @@
       <c r="G738" s="3"/>
       <c r="H738" s="3"/>
     </row>
-    <row r="739" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B739" s="3"/>
       <c r="C739" s="3"/>
       <c r="D739" s="3"/>
@@ -7986,7 +7776,7 @@
       <c r="G739" s="3"/>
       <c r="H739" s="3"/>
     </row>
-    <row r="740" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B740" s="3"/>
       <c r="C740" s="3"/>
       <c r="D740" s="3"/>
@@ -7995,7 +7785,7 @@
       <c r="G740" s="3"/>
       <c r="H740" s="3"/>
     </row>
-    <row r="741" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B741" s="3"/>
       <c r="C741" s="3"/>
       <c r="D741" s="3"/>
@@ -8004,7 +7794,7 @@
       <c r="G741" s="3"/>
       <c r="H741" s="3"/>
     </row>
-    <row r="742" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B742" s="3"/>
       <c r="C742" s="3"/>
       <c r="D742" s="3"/>
@@ -8013,20 +7803,20 @@
       <c r="G742" s="3"/>
       <c r="H742" s="3"/>
     </row>
-    <row r="747" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A747" s="2"/>
     </row>
-    <row r="748" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A748" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="S8:T8"/>
     <mergeCell ref="B2:H3"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="G63:H63"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="G61:H61"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="S4:T4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B5:E56 G5:H56">
@@ -8037,7 +7827,7 @@
       <formula>#REF!=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations xWindow="1141" yWindow="341" count="7">
+  <dataValidations disablePrompts="1" xWindow="1141" yWindow="341" count="7">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Insira o nome do item nesta coluna" sqref="B4" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Insira o nível de estoque de cada item nesta coluna" sqref="G4" xr:uid="{00000000-0002-0000-0000-000007000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Esse é um valor de estoque column._x000a__x000a_O valor de estoque de cada item é automaticamente calculado nesta coluna." sqref="F4" xr:uid="{00000000-0002-0000-0000-000008000000}"/>
@@ -8059,128 +7849,128 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D863DC5D-F27E-48D0-B8DF-8044B97C94FB}">
   <dimension ref="A1:G71"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="73" customWidth="1"/>
-    <col min="2" max="2" width="140.625" customWidth="1"/>
-    <col min="3" max="3" width="20.125" customWidth="1"/>
+    <col min="2" max="2" width="140.59765625" customWidth="1"/>
+    <col min="3" max="3" width="20.09765625" customWidth="1"/>
     <col min="4" max="4" width="13.5" customWidth="1"/>
     <col min="5" max="5" width="15.5" customWidth="1"/>
-    <col min="6" max="6" width="14.625" customWidth="1"/>
+    <col min="6" max="6" width="14.59765625" customWidth="1"/>
     <col min="7" max="7" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="79" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-    </row>
-    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="70"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-    </row>
-    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-    </row>
-    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="70"/>
-      <c r="B4" s="70"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-    </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="70"/>
-      <c r="B5" s="70"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-    </row>
-    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="70"/>
-      <c r="B6" s="70"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-    </row>
-    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="70"/>
-      <c r="B7" s="70"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-    </row>
-    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="70"/>
-      <c r="B8" s="70"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-    </row>
-    <row r="9" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+    </row>
+    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+    </row>
+    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="79"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+    </row>
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="79"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+    </row>
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="79"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+    </row>
+    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="79"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+    </row>
+    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="79"/>
+      <c r="B7" s="79"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="79"/>
+      <c r="G7" s="79"/>
+    </row>
+    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="79"/>
+      <c r="B8" s="79"/>
+      <c r="C8" s="79"/>
+      <c r="D8" s="79"/>
+      <c r="E8" s="79"/>
+      <c r="F8" s="79"/>
+      <c r="G8" s="79"/>
+    </row>
+    <row r="9" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="42" t="s">
+      <c r="F9" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="42" t="s">
+      <c r="G9" s="37" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A10" s="39" t="s">
+    <row r="10" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A10" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="36">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8188,27 +7978,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>13</v>
       </c>
-      <c r="F10" s="39">
+      <c r="F10" s="34">
         <v>1</v>
       </c>
-      <c r="G10" s="39" t="s">
+      <c r="G10" s="34" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A11" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="38">
+      <c r="E11" s="33">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8216,27 +8006,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="31">
         <v>1</v>
       </c>
-      <c r="G11" s="36" t="s">
+      <c r="G11" s="31" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
+    <row r="12" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A12" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="D12" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="36">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8244,27 +8034,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="F12" s="39">
+      <c r="F12" s="34">
         <v>2</v>
       </c>
-      <c r="G12" s="39" t="s">
+      <c r="G12" s="34" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A13" s="36" t="s">
+    <row r="13" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A13" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="38">
+      <c r="E13" s="33">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8272,27 +8062,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>13</v>
       </c>
-      <c r="F13" s="36">
+      <c r="F13" s="31">
         <v>2</v>
       </c>
-      <c r="G13" s="36" t="s">
+      <c r="G13" s="31" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A14" s="39" t="s">
+    <row r="14" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A14" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="36">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8300,27 +8090,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>3</v>
       </c>
-      <c r="F14" s="39">
+      <c r="F14" s="34">
         <v>1</v>
       </c>
-      <c r="G14" s="39" t="s">
+      <c r="G14" s="34" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A15" s="36" t="s">
+    <row r="15" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A15" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="36" t="s">
+      <c r="D15" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="38">
+      <c r="E15" s="33">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8328,27 +8118,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="31">
         <v>2</v>
       </c>
-      <c r="G15" s="36" t="s">
+      <c r="G15" s="31" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A16" s="39" t="s">
+    <row r="16" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A16" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="36">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8356,27 +8146,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="F16" s="39">
+      <c r="F16" s="34">
         <v>1</v>
       </c>
-      <c r="G16" s="39" t="s">
+      <c r="G16" s="34" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A17" s="36" t="s">
+    <row r="17" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A17" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C17" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="36" t="s">
+      <c r="D17" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="38">
+      <c r="E17" s="33">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8384,27 +8174,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="F17" s="36">
+      <c r="F17" s="31">
         <v>3</v>
       </c>
-      <c r="G17" s="36" t="s">
+      <c r="G17" s="31" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+    <row r="18" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A18" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="41">
+      <c r="E18" s="36">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8412,27 +8202,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="F18" s="39">
+      <c r="F18" s="34">
         <v>1</v>
       </c>
-      <c r="G18" s="39" t="s">
+      <c r="G18" s="34" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A19" s="36" t="s">
+    <row r="19" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A19" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="37" t="s">
+      <c r="C19" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="36" t="s">
+      <c r="D19" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="38">
+      <c r="E19" s="33">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8440,27 +8230,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>13</v>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="31">
         <v>3</v>
       </c>
-      <c r="G19" s="36" t="s">
+      <c r="G19" s="31" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A20" s="39" t="s">
+    <row r="20" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A20" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="39" t="s">
+      <c r="D20" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="41">
+      <c r="E20" s="36">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8468,27 +8258,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="F20" s="39">
+      <c r="F20" s="34">
         <v>2</v>
       </c>
-      <c r="G20" s="39" t="s">
+      <c r="G20" s="34" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A21" s="36" t="s">
+    <row r="21" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A21" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="36" t="s">
+      <c r="B21" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="37" t="s">
+      <c r="C21" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="36" t="s">
+      <c r="D21" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="38">
+      <c r="E21" s="33">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8496,27 +8286,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="31">
         <v>2</v>
       </c>
-      <c r="G21" s="36" t="s">
+      <c r="G21" s="31" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A22" s="39" t="s">
+    <row r="22" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A22" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="39" t="s">
+      <c r="B22" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="39" t="s">
+      <c r="D22" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="E22" s="41">
+      <c r="E22" s="36">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8524,27 +8314,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="F22" s="39">
+      <c r="F22" s="34">
         <v>2</v>
       </c>
-      <c r="G22" s="39" t="s">
+      <c r="G22" s="34" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A23" s="36" t="s">
+    <row r="23" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A23" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="36" t="s">
+      <c r="B23" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="37" t="s">
+      <c r="C23" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="36" t="s">
+      <c r="D23" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="38">
+      <c r="E23" s="33">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8552,27 +8342,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="F23" s="36">
+      <c r="F23" s="31">
         <v>3</v>
       </c>
-      <c r="G23" s="36" t="s">
+      <c r="G23" s="31" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A24" s="39" t="s">
+    <row r="24" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A24" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="39" t="s">
+      <c r="D24" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="E24" s="41">
+      <c r="E24" s="36">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8580,27 +8370,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="F24" s="39">
+      <c r="F24" s="34">
         <v>1</v>
       </c>
-      <c r="G24" s="39" t="s">
+      <c r="G24" s="34" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A25" s="36" t="s">
+    <row r="25" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A25" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="B25" s="36" t="s">
+      <c r="B25" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="37" t="s">
+      <c r="C25" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="36" t="s">
+      <c r="D25" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="38">
+      <c r="E25" s="33">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8608,27 +8398,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="F25" s="36">
+      <c r="F25" s="31">
         <v>1</v>
       </c>
-      <c r="G25" s="36" t="s">
+      <c r="G25" s="31" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A26" s="39" t="s">
+    <row r="26" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A26" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="39" t="s">
+      <c r="D26" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="41">
+      <c r="E26" s="36">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8636,27 +8426,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="F26" s="39">
+      <c r="F26" s="34">
         <v>3</v>
       </c>
-      <c r="G26" s="39" t="s">
+      <c r="G26" s="34" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A27" s="36" t="s">
+    <row r="27" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A27" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="37" t="s">
+      <c r="C27" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="36" t="s">
+      <c r="D27" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E27" s="38">
+      <c r="E27" s="33">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8664,27 +8454,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="F27" s="36">
+      <c r="F27" s="31">
         <v>1</v>
       </c>
-      <c r="G27" s="36" t="s">
+      <c r="G27" s="31" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A28" s="39" t="s">
+    <row r="28" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A28" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="B28" s="39" t="s">
+      <c r="B28" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="C28" s="40" t="s">
+      <c r="C28" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="39" t="s">
+      <c r="D28" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="E28" s="41">
+      <c r="E28" s="36">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8692,27 +8482,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="F28" s="39">
+      <c r="F28" s="34">
         <v>2</v>
       </c>
-      <c r="G28" s="39" t="s">
+      <c r="G28" s="34" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A29" s="36" t="s">
+    <row r="29" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A29" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="B29" s="36" t="s">
+      <c r="B29" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="C29" s="37" t="s">
+      <c r="C29" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="36" t="s">
+      <c r="D29" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E29" s="38">
+      <c r="E29" s="33">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8720,27 +8510,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="F29" s="36">
+      <c r="F29" s="31">
         <v>3</v>
       </c>
-      <c r="G29" s="36" t="s">
+      <c r="G29" s="31" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A30" s="39" t="s">
+    <row r="30" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A30" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="40" t="s">
+      <c r="C30" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="D30" s="39" t="s">
+      <c r="D30" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="E30" s="41">
+      <c r="E30" s="36">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8748,27 +8538,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="F30" s="39">
+      <c r="F30" s="34">
         <v>3</v>
       </c>
-      <c r="G30" s="39" t="s">
+      <c r="G30" s="34" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A31" s="36" t="s">
+    <row r="31" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A31" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="B31" s="36" t="s">
+      <c r="B31" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="C31" s="37" t="s">
+      <c r="C31" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D31" s="36" t="s">
+      <c r="D31" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="E31" s="38">
+      <c r="E31" s="33">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8776,27 +8566,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>3</v>
       </c>
-      <c r="F31" s="36">
+      <c r="F31" s="31">
         <v>2</v>
       </c>
-      <c r="G31" s="36" t="s">
+      <c r="G31" s="31" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A32" s="39" t="s">
+    <row r="32" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A32" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="B32" s="39" t="s">
+      <c r="B32" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="C32" s="40" t="s">
+      <c r="C32" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="39" t="s">
+      <c r="D32" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E32" s="41">
+      <c r="E32" s="36">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8804,27 +8594,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>13</v>
       </c>
-      <c r="F32" s="39">
+      <c r="F32" s="34">
         <v>3</v>
       </c>
-      <c r="G32" s="39" t="s">
+      <c r="G32" s="34" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A33" s="36" t="s">
+    <row r="33" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A33" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="B33" s="36" t="s">
+      <c r="B33" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="37" t="s">
+      <c r="C33" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="36" t="s">
+      <c r="D33" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="E33" s="38">
+      <c r="E33" s="33">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8832,27 +8622,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>13</v>
       </c>
-      <c r="F33" s="36">
+      <c r="F33" s="31">
         <v>3</v>
       </c>
-      <c r="G33" s="36" t="s">
+      <c r="G33" s="31" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A34" s="39" t="s">
+    <row r="34" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A34" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="B34" s="39" t="s">
+      <c r="B34" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="C34" s="40" t="s">
+      <c r="C34" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="D34" s="39" t="s">
+      <c r="D34" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="E34" s="41">
+      <c r="E34" s="36">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8860,27 +8650,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>8</v>
       </c>
-      <c r="F34" s="39">
+      <c r="F34" s="34">
         <v>3</v>
       </c>
-      <c r="G34" s="39" t="s">
+      <c r="G34" s="34" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A35" s="36" t="s">
+    <row r="35" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A35" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="B35" s="36" t="s">
+      <c r="B35" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="37" t="s">
+      <c r="C35" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="D35" s="36" t="s">
+      <c r="D35" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E35" s="38">
+      <c r="E35" s="33">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8888,27 +8678,27 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="F35" s="36">
+      <c r="F35" s="31">
         <v>2</v>
       </c>
-      <c r="G35" s="36" t="s">
+      <c r="G35" s="31" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A36" s="39" t="s">
+    <row r="36" spans="1:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="A36" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="B36" s="39" t="s">
+      <c r="B36" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="40" t="s">
+      <c r="C36" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="D36" s="39" t="s">
+      <c r="D36" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="E36" s="41">
+      <c r="E36" s="36">
         <f>IF(Tabela33[[#This Row],[Tamanho]]="PP",3,
 IF(Tabela33[[#This Row],[Tamanho]]="P",5,
 IF(Tabela33[[#This Row],[Tamanho]]="M",8,
@@ -8916,132 +8706,132 @@
 IF(Tabela33[[#This Row],[Tamanho]]="GG",21,0)))))</f>
         <v>5</v>
       </c>
-      <c r="F36" s="39">
+      <c r="F36" s="34">
         <v>2</v>
       </c>
-      <c r="G36" s="39" t="s">
+      <c r="G36" s="34" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="71"/>
-      <c r="B37" s="71"/>
-      <c r="C37" s="63"/>
-      <c r="D37" s="63"/>
-      <c r="E37" s="63"/>
-      <c r="F37" s="63"/>
-      <c r="G37" s="63"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="71"/>
-      <c r="B38" s="71"/>
-      <c r="C38" s="63"/>
-      <c r="D38" s="63"/>
-      <c r="E38" s="63"/>
-      <c r="F38" s="63"/>
-      <c r="G38" s="63"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="71"/>
-      <c r="B39" s="71"/>
-      <c r="C39" s="63"/>
-      <c r="D39" s="63"/>
-      <c r="E39" s="63"/>
-      <c r="F39" s="63"/>
-      <c r="G39" s="63"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="71"/>
-      <c r="B40" s="71"/>
-      <c r="C40" s="63"/>
-      <c r="D40" s="63"/>
-      <c r="E40" s="63"/>
-      <c r="F40" s="63"/>
-      <c r="G40" s="63"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="71"/>
-      <c r="B41" s="71"/>
-      <c r="C41" s="63"/>
-      <c r="D41" s="63"/>
-      <c r="E41" s="63"/>
-      <c r="F41" s="63"/>
-      <c r="G41" s="63"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="71"/>
-      <c r="B42" s="71"/>
-      <c r="C42" s="63"/>
-      <c r="D42" s="63"/>
-      <c r="E42" s="63"/>
-      <c r="F42" s="63"/>
-      <c r="G42" s="63"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="71"/>
-      <c r="B43" s="71"/>
-      <c r="C43" s="63"/>
-      <c r="D43" s="63"/>
-      <c r="E43" s="63"/>
-      <c r="F43" s="63"/>
-      <c r="G43" s="63"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="71"/>
-      <c r="B44" s="71"/>
-      <c r="C44" s="63"/>
-      <c r="D44" s="63"/>
-      <c r="E44" s="63"/>
-      <c r="F44" s="63"/>
-      <c r="G44" s="63"/>
-    </row>
-    <row r="45" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="71"/>
-      <c r="B45" s="71"/>
-      <c r="C45" s="63"/>
-      <c r="D45" s="63"/>
-      <c r="E45" s="63"/>
-      <c r="F45" s="63"/>
-      <c r="G45" s="63"/>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="71"/>
-      <c r="B46" s="71"/>
-      <c r="C46" s="30"/>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="80"/>
+      <c r="B37" s="80"/>
+      <c r="C37" s="72"/>
+      <c r="D37" s="72"/>
+      <c r="E37" s="72"/>
+      <c r="F37" s="72"/>
+      <c r="G37" s="72"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="80"/>
+      <c r="B38" s="80"/>
+      <c r="C38" s="72"/>
+      <c r="D38" s="72"/>
+      <c r="E38" s="72"/>
+      <c r="F38" s="72"/>
+      <c r="G38" s="72"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="80"/>
+      <c r="B39" s="80"/>
+      <c r="C39" s="72"/>
+      <c r="D39" s="72"/>
+      <c r="E39" s="72"/>
+      <c r="F39" s="72"/>
+      <c r="G39" s="72"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="80"/>
+      <c r="B40" s="80"/>
+      <c r="C40" s="72"/>
+      <c r="D40" s="72"/>
+      <c r="E40" s="72"/>
+      <c r="F40" s="72"/>
+      <c r="G40" s="72"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="80"/>
+      <c r="B41" s="80"/>
+      <c r="C41" s="72"/>
+      <c r="D41" s="72"/>
+      <c r="E41" s="72"/>
+      <c r="F41" s="72"/>
+      <c r="G41" s="72"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="80"/>
+      <c r="B42" s="80"/>
+      <c r="C42" s="72"/>
+      <c r="D42" s="72"/>
+      <c r="E42" s="72"/>
+      <c r="F42" s="72"/>
+      <c r="G42" s="72"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="80"/>
+      <c r="B43" s="80"/>
+      <c r="C43" s="72"/>
+      <c r="D43" s="72"/>
+      <c r="E43" s="72"/>
+      <c r="F43" s="72"/>
+      <c r="G43" s="72"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="80"/>
+      <c r="B44" s="80"/>
+      <c r="C44" s="72"/>
+      <c r="D44" s="72"/>
+      <c r="E44" s="72"/>
+      <c r="F44" s="72"/>
+      <c r="G44" s="72"/>
+    </row>
+    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="80"/>
+      <c r="B45" s="80"/>
+      <c r="C45" s="72"/>
+      <c r="D45" s="72"/>
+      <c r="E45" s="72"/>
+      <c r="F45" s="72"/>
+      <c r="G45" s="72"/>
+    </row>
+    <row r="46" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="80"/>
+      <c r="B46" s="80"/>
+      <c r="C46" s="28"/>
       <c r="D46" s="12" t="s">
         <v>117</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="F46" s="72" t="s">
+      <c r="F46" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="G46" s="73"/>
-    </row>
-    <row r="47" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="71"/>
-      <c r="B47" s="71"/>
+      <c r="G46" s="82"/>
+    </row>
+    <row r="47" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="80"/>
+      <c r="B47" s="80"/>
       <c r="C47" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="D47" s="44">
+      <c r="D47" s="39">
         <f>SUM(E10:E36)</f>
         <v>201</v>
       </c>
-      <c r="E47" s="44">
+      <c r="E47" s="39">
         <f>SUM(E48:E51)</f>
         <v>201</v>
       </c>
-      <c r="F47" s="74">
+      <c r="F47" s="83">
         <f>D47-E47</f>
         <v>0</v>
       </c>
-      <c r="G47" s="75"/>
-    </row>
-    <row r="48" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="71"/>
-      <c r="B48" s="71"/>
+      <c r="G47" s="84"/>
+    </row>
+    <row r="48" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="80"/>
+      <c r="B48" s="80"/>
       <c r="C48" s="14" t="s">
         <v>123</v>
       </c>
@@ -9053,14 +8843,14 @@
         <f>SUM(E10:E11,E14,E24,E25)</f>
         <v>37</v>
       </c>
-      <c r="F48" s="59">
+      <c r="F48" s="68">
         <v>0</v>
       </c>
-      <c r="G48" s="60"/>
-    </row>
-    <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="71"/>
-      <c r="B49" s="71"/>
+      <c r="G48" s="69"/>
+    </row>
+    <row r="49" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="80"/>
+      <c r="B49" s="80"/>
       <c r="C49" s="14" t="s">
         <v>120</v>
       </c>
@@ -9072,15 +8862,15 @@
         <f>SUM(E12,E13,E20,E21,E22,E27,E28,E29)</f>
         <v>57</v>
       </c>
-      <c r="F49" s="59">
+      <c r="F49" s="68">
         <f>D49-E49</f>
         <v>0</v>
       </c>
-      <c r="G49" s="60"/>
-    </row>
-    <row r="50" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="71"/>
-      <c r="B50" s="71"/>
+      <c r="G49" s="69"/>
+    </row>
+    <row r="50" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="80"/>
+      <c r="B50" s="80"/>
       <c r="C50" s="14" t="s">
         <v>122</v>
       </c>
@@ -9092,15 +8882,15 @@
         <f>SUM(E15,E17,E18,E19,E26,E30,E31,E32)</f>
         <v>63</v>
       </c>
-      <c r="F50" s="59">
+      <c r="F50" s="68">
         <f>D50-E50</f>
         <v>0</v>
       </c>
-      <c r="G50" s="60"/>
-    </row>
-    <row r="51" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="71"/>
-      <c r="B51" s="71"/>
+      <c r="G50" s="69"/>
+    </row>
+    <row r="51" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="80"/>
+      <c r="B51" s="80"/>
       <c r="C51" s="14" t="s">
         <v>121</v>
       </c>
@@ -9112,105 +8902,105 @@
         <f>SUM(E16,E23,E34,E35,E36,E33)</f>
         <v>44</v>
       </c>
-      <c r="F51" s="59">
+      <c r="F51" s="68">
         <f>D51-E51</f>
         <v>0</v>
       </c>
-      <c r="G51" s="60"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="71"/>
-      <c r="B52" s="71"/>
-      <c r="C52" s="76"/>
-      <c r="D52" s="76"/>
-      <c r="E52" s="76"/>
-      <c r="F52" s="48"/>
-      <c r="G52" s="48"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="71"/>
-      <c r="B53" s="71"/>
-      <c r="C53" s="63"/>
-      <c r="D53" s="63"/>
-      <c r="E53" s="63"/>
-      <c r="F53" s="52"/>
-      <c r="G53" s="52"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="71"/>
-      <c r="B54" s="71"/>
-      <c r="C54" s="63"/>
-      <c r="D54" s="63"/>
-      <c r="E54" s="63"/>
-      <c r="F54" s="52"/>
-      <c r="G54" s="52"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="71"/>
-      <c r="B55" s="71"/>
-      <c r="C55" s="63"/>
-      <c r="D55" s="63"/>
-      <c r="E55" s="63"/>
-      <c r="F55" s="52"/>
-      <c r="G55" s="52"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="71"/>
-      <c r="B56" s="71"/>
-      <c r="C56" s="63"/>
-      <c r="D56" s="63"/>
-      <c r="E56" s="63"/>
-      <c r="F56" s="52"/>
-      <c r="G56" s="52"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="71"/>
-      <c r="B57" s="71"/>
-      <c r="C57" s="63"/>
-      <c r="D57" s="63"/>
-      <c r="E57" s="63"/>
-      <c r="F57" s="52"/>
-      <c r="G57" s="52"/>
-    </row>
-    <row r="58" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="71"/>
-      <c r="B58" s="71"/>
-      <c r="C58" s="63"/>
-      <c r="D58" s="63"/>
-      <c r="E58" s="63"/>
-      <c r="F58" s="52"/>
-      <c r="G58" s="52"/>
-    </row>
-    <row r="59" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="71"/>
-      <c r="B59" s="71"/>
-      <c r="C59" s="30"/>
+      <c r="G51" s="69"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="80"/>
+      <c r="B52" s="80"/>
+      <c r="C52" s="85"/>
+      <c r="D52" s="85"/>
+      <c r="E52" s="85"/>
+      <c r="F52" s="43"/>
+      <c r="G52" s="43"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="80"/>
+      <c r="B53" s="80"/>
+      <c r="C53" s="72"/>
+      <c r="D53" s="72"/>
+      <c r="E53" s="72"/>
+      <c r="F53" s="47"/>
+      <c r="G53" s="47"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="80"/>
+      <c r="B54" s="80"/>
+      <c r="C54" s="72"/>
+      <c r="D54" s="72"/>
+      <c r="E54" s="72"/>
+      <c r="F54" s="47"/>
+      <c r="G54" s="47"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="80"/>
+      <c r="B55" s="80"/>
+      <c r="C55" s="72"/>
+      <c r="D55" s="72"/>
+      <c r="E55" s="72"/>
+      <c r="F55" s="47"/>
+      <c r="G55" s="47"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="80"/>
+      <c r="B56" s="80"/>
+      <c r="C56" s="72"/>
+      <c r="D56" s="72"/>
+      <c r="E56" s="72"/>
+      <c r="F56" s="47"/>
+      <c r="G56" s="47"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="80"/>
+      <c r="B57" s="80"/>
+      <c r="C57" s="72"/>
+      <c r="D57" s="72"/>
+      <c r="E57" s="72"/>
+      <c r="F57" s="47"/>
+      <c r="G57" s="47"/>
+    </row>
+    <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="80"/>
+      <c r="B58" s="80"/>
+      <c r="C58" s="72"/>
+      <c r="D58" s="72"/>
+      <c r="E58" s="72"/>
+      <c r="F58" s="47"/>
+      <c r="G58" s="47"/>
+    </row>
+    <row r="59" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="80"/>
+      <c r="B59" s="80"/>
+      <c r="C59" s="28"/>
       <c r="D59" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="E59" s="63"/>
-      <c r="F59" s="64" t="s">
+      <c r="E59" s="72"/>
+      <c r="F59" s="73" t="s">
         <v>136</v>
       </c>
-      <c r="G59" s="65"/>
-    </row>
-    <row r="60" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="71"/>
-      <c r="B60" s="71"/>
+      <c r="G59" s="74"/>
+    </row>
+    <row r="60" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A60" s="80"/>
+      <c r="B60" s="80"/>
       <c r="C60" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="D60" s="44">
+      <c r="D60" s="39">
         <f>SUM(E10:E36)</f>
         <v>201</v>
       </c>
-      <c r="E60" s="63"/>
-      <c r="F60" s="66"/>
-      <c r="G60" s="67"/>
-    </row>
-    <row r="61" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="71"/>
-      <c r="B61" s="71"/>
+      <c r="E60" s="72"/>
+      <c r="F60" s="75"/>
+      <c r="G60" s="76"/>
+    </row>
+    <row r="61" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="80"/>
+      <c r="B61" s="80"/>
       <c r="C61" s="14" t="s">
         <v>123</v>
       </c>
@@ -9218,13 +9008,13 @@
         <f>D60-D48</f>
         <v>164</v>
       </c>
-      <c r="E61" s="63"/>
-      <c r="F61" s="68"/>
-      <c r="G61" s="69"/>
-    </row>
-    <row r="62" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="71"/>
-      <c r="B62" s="71"/>
+      <c r="E61" s="72"/>
+      <c r="F61" s="77"/>
+      <c r="G61" s="78"/>
+    </row>
+    <row r="62" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="80"/>
+      <c r="B62" s="80"/>
       <c r="C62" s="14" t="s">
         <v>120</v>
       </c>
@@ -9232,17 +9022,17 @@
         <f>D61-D49</f>
         <v>107</v>
       </c>
-      <c r="E62" s="63"/>
-      <c r="F62" s="49" t="s">
+      <c r="E62" s="72"/>
+      <c r="F62" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="G62" s="50" t="s">
+      <c r="G62" s="45" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="71"/>
-      <c r="B63" s="71"/>
+    <row r="63" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="80"/>
+      <c r="B63" s="80"/>
       <c r="C63" s="14" t="s">
         <v>122</v>
       </c>
@@ -9250,18 +9040,18 @@
         <f>D62-E50</f>
         <v>44</v>
       </c>
-      <c r="E63" s="63"/>
-      <c r="F63" s="45" t="s">
+      <c r="E63" s="72"/>
+      <c r="F63" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="G63" s="43">
+      <c r="G63" s="38">
         <f>VLOOKUP(G62,C46:G51,3,FALSE)</f>
         <v>37</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="71"/>
-      <c r="B64" s="71"/>
+    <row r="64" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A64" s="80"/>
+      <c r="B64" s="80"/>
       <c r="C64" s="14" t="s">
         <v>121</v>
       </c>
@@ -9269,62 +9059,62 @@
         <f>D51+F50-E51</f>
         <v>0</v>
       </c>
-      <c r="E64" s="63"/>
-      <c r="F64" s="45" t="s">
+      <c r="E64" s="72"/>
+      <c r="F64" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="G64" s="43">
+      <c r="G64" s="38">
         <f>VLOOKUP(G62,C46:G51,2,FALSE)</f>
         <v>37</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="71"/>
-      <c r="B65" s="71"/>
-      <c r="C65" s="63"/>
-      <c r="D65" s="63"/>
-      <c r="E65" s="63"/>
-      <c r="F65" s="63"/>
-      <c r="G65" s="63"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="71"/>
-      <c r="B66" s="71"/>
-      <c r="C66" s="63"/>
-      <c r="D66" s="63"/>
-      <c r="E66" s="63"/>
-      <c r="F66" s="63"/>
-      <c r="G66" s="63"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="71"/>
-      <c r="B67" s="71"/>
-      <c r="C67" s="63"/>
-      <c r="D67" s="63"/>
-      <c r="E67" s="63"/>
-      <c r="F67" s="63"/>
-      <c r="G67" s="63"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="71"/>
-      <c r="B68" s="71"/>
-      <c r="C68" s="63"/>
-      <c r="D68" s="63"/>
-      <c r="E68" s="63"/>
-      <c r="F68" s="63"/>
-      <c r="G68" s="63"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="71"/>
-      <c r="B69" s="71"/>
-      <c r="C69" s="63"/>
-      <c r="D69" s="63"/>
-      <c r="E69" s="63"/>
-      <c r="F69" s="63"/>
-      <c r="G69" s="63"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B71" s="51"/>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="80"/>
+      <c r="B65" s="80"/>
+      <c r="C65" s="72"/>
+      <c r="D65" s="72"/>
+      <c r="E65" s="72"/>
+      <c r="F65" s="72"/>
+      <c r="G65" s="72"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="80"/>
+      <c r="B66" s="80"/>
+      <c r="C66" s="72"/>
+      <c r="D66" s="72"/>
+      <c r="E66" s="72"/>
+      <c r="F66" s="72"/>
+      <c r="G66" s="72"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="80"/>
+      <c r="B67" s="80"/>
+      <c r="C67" s="72"/>
+      <c r="D67" s="72"/>
+      <c r="E67" s="72"/>
+      <c r="F67" s="72"/>
+      <c r="G67" s="72"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="80"/>
+      <c r="B68" s="80"/>
+      <c r="C68" s="72"/>
+      <c r="D68" s="72"/>
+      <c r="E68" s="72"/>
+      <c r="F68" s="72"/>
+      <c r="G68" s="72"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="80"/>
+      <c r="B69" s="80"/>
+      <c r="C69" s="72"/>
+      <c r="D69" s="72"/>
+      <c r="E69" s="72"/>
+      <c r="F69" s="72"/>
+      <c r="G69" s="72"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B71" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -9566,15 +9356,15 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E347ADB8-BE75-4F14-ADF9-E64D4A3FD476}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="8497f9ae-9c71-438c-b553-1e6fe8b1acb0"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="8497f9ae-9c71-438c-b553-1e6fe8b1acb0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
